--- a/specs/docs/workbook.xlsx
+++ b/specs/docs/workbook.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="18.005" customWidth="1" style="1" min="1" max="1"/>
@@ -612,6 +612,40 @@
       <c r="C9" t="inlineStr">
         <is>
           <t>Production Planning (eksternal, read-only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Master Material</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Data master material (Berat/Meter dll.) untuk costing dan unpack</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Engineering (first pass, belum dikonfirmasi klien)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Master rate, BOM, flow process, price reference, kurs dan simulasi costing/pricelist</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Accounting (first pass, belum dikonfirmasi klien)</t>
         </is>
       </c>
     </row>
@@ -833,12 +867,13 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Master Product (sesuai SPK); Baby Coil hasil Add Coil (bisa &gt;1); Qty; pilihan metode berat (Pilihan 1: Qty x Berat Standard/pcs, atau Pilihan 2: input Kg langsung); Berat Standard/pcs (database)</t>
+          <t>Master Product (sesuai SPK); Baby Coil hasil Add Coil (bisa &gt;1); Qty; pilihan metode berat (Pilihan 1: Qty x Berat Standard/pcs, atau Pilihan 2: input Kg langsung); Berat Standard/pcs (dihitung: Berat/Meter varian BOM × Panjang produk)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>FR-09: Admin Produksi menginput Detail Produksi untuk Finish Good KW 1 per baby coil yang sudah di-add (bisa &gt;1 baby coil per produk), dengan dua pilihan metode input berat: Pilihan 1 (Qty x Berat Standard/pcs dari database) atau Pilihan 2 (input Kg langsung, sistem hitung Berat/Pcs = Total Berat / Qty). Kedua pilihan menghasilkan %Selisih = (Berat/pcs - Berat Standard/pcs) / Berat Standard/pcs, dan sistem menampilkan popup notifikasi cek ulang bila selisih melebihi ± 0,7%.</t>
+          <t>FR-09: Admin Produksi menginput Detail Produksi untuk Finish Good KW 1 per baby coil yang sudah di-add (bisa &gt;1 baby coil per produk), dengan dua pilihan metode input berat: Pilihan 1 (Qty x Berat Standard/pcs dari database) atau Pilihan 2 (input Kg langsung, sistem hitung Berat/Pcs = Total Berat / Qty). Kedua pilihan menghasilkan %Selisih = (Berat/pcs - Berat Standard/pcs) / Berat Standard/pcs, dan sistem menampilkan popup notifikasi cek ulang bila selisih melebihi ± 0,7%.
+Diubah 2026-10-07: Berat Standard/pcs bukan kolom database produk, melainkan hasil perhitungan = Berat/Meter varian BOM yang dipilih × Panjang produk (FR-37, FR-46); nilainya tersimpan ke berat_standard pada item laporan.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1170,7 +1205,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="10.005" customWidth="1" style="1" min="1" max="1"/>
@@ -1296,7 +1331,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>FR-10: Admin Produksi dapat mencatat Stok Bebas untuk sisa coil yang dijadikan produk di luar SPK (bukan hasil SPK yang sedang berjalan), dengan alur input yang identik dengan FR-09 (pilihan Master Product, baby coil sumber, dua pilihan input berat, %Selisih, popup toleransi).
+          <t>FR-10: Admin Produksi dapat mencatat Stok Bebas untuk sisa coil yang dijadikan produk di luar SPK (bukan hasil SPK yang sedang berjalan), dengan alur input yang identik dengan FR-09 (pilihan Master Product, baby coil sumber, dua pilihan input berat, %Selisih, popup toleransi). Berat Standard/pcs dihitung dari Berat/Meter varian BOM × Panjang produk (lihat FR-09, diubah 2026-10-07).
 Dipisah dari UC-04 (Input Jumlah FG KW1) karena tujuan aktor berbeda — mencatat produk di luar SPK, bukan hasil SPK yang berjalan — meski dilakukan dalam sesi Laporan Produksi yang sama.</t>
         </is>
       </c>
@@ -1393,6 +1428,479 @@
       <c r="H5" s="3" t="inlineStr">
         <is>
           <t>warehouse_stock, baby_coil</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>UC-N05</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Kelola Master Produk</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Master Product</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Level 1 Product Type; Level 2 Product Category; Level 3 Product Jenis; Level 4 Product Master (nama produk); Lebar; Tebal; Panjang (meter)</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>FR-37: Master Produk menyimpan hierarki 4 level (Level 1 Product Type, Level 2 Product Category, Level 3 Product Jenis, Level 4 Product Master/nama produk) dan Lebar (tetap per produk, karena satu lebar bisa memakai ketebalan material berbeda). Tebal dan Panjang (meter) tetap disimpan di Master Produk (keputusan user 2026-10-07, open question 3; menggantikan catatan sheet Ide E9–E11). Berat per Pcs tidak disimpan di produk: = Berat/Meter varian BOM × Panjang produk (FR-46). Contoh user: Produk 1 panjang 6 m; material A 1 kg/m → 6 kg, material B 1,3 kg/m → 7,8 kg.
+Sub-flow:
+1. Engineering membuka daftar Master Produk.
+2. Engineering menambah/mengubah/menghapus produk: mengisi hierarki 4 level, Lebar, Tebal, dan Panjang (meter).
+3. Sistem menyimpan dan menampilkan kembali daftar produk. (Berat per Pcs tidak diisi di sini — diturunkan dari Berat/Meter varian BOM × Panjang.)
+Keputusan user 2026-10-07: master data dibangun dan diisi lewat UI sistem ini. Open question 3 resolved: Tebal dan Panjang tetap ada di Master Produk; berat per pcs = Berat/Meter varian BOM × Panjang. Aktor ditetapkan user 2026-10-07 (open question 10).</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Produk (hierarki 4 level, Lebar, Tebal, Panjang) tersimpan dan tampil di daftar Master Produk</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>product_lvl_4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>UC-N06</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Kelola Master Material</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Master Material</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Metal Type; Slitted/Non Slit; Boron/Non Boron; Material Name; Width; Thickness; Berat/Meter (kg/m)</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>FR-38: Master Material menyimpan Metal Type, Slitted/Non Slit, Boron/Non Boron, Material Name, Width, Thickness, dan Berat/Meter (kg/m). Berat/Meter ditambahkan ke master karena dibutuhkan untuk konversi biaya dari Rp/Kg ke Rp/meter (catatan sheet Simulasi Program, I10), dan dipakai per varian BOM untuk menghitung Berat per Pcs. Contoh baris di sheet menulis Width 914 untuk material "…-1219-…"; itu salah ketik, nilai yang benar 1219 (input/2026-10-07-product-costing-jawaban/).
+Sub-flow:
+1. Engineering membuka daftar Master Material.
+2. Engineering menambah/mengubah/menghapus material dengan mengisi atribut di atas, termasuk Berat/Meter.
+3. Sistem menyimpan dan menampilkan kembali daftar material.
+Keputusan user 2026-10-07: master data dibangun dan diisi lewat UI sistem ini. Open question 8 resolved: Width yang benar 1219 (salah ketik pada contoh). Aktor ditetapkan user 2026-10-07 (open question 10).</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Material (termasuk Berat/Meter) tersimpan dan tampil di daftar Master Material</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>UC-N07</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Kelola Kurs</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Currency; Kurs</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>FR-39: Master Kurs menyimpan Currency, Kurs, Last Updated, dan Updated By. Kurs dipakai mengubah Price Reference dari USD ke Rupiah.
+Sub-flow:
+1. Accounting membuka daftar Kurs.
+2. Accounting menambah/mengubah/menghapus Currency dan nilai Kurs.
+3. Sistem mengisi Last Updated dan Updated By, lalu menampilkan kembali daftar.
+Keputusan user 2026-10-07: master data dibangun dan diisi lewat UI sistem ini. Kurs dipakai oleh UC-N08 untuk mengubah Price Reference USD ke Rupiah. Aktor Accounting sesuai kolom Updated By pada sumber.</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Kurs tersimpan dengan Last Updated dan Updated By; tampil di daftar Kurs</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>master_kurs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>UC-N08</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Kelola Price Reference</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Purchasing</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Material; Harga pembelian per bulan (USD/kg); Keputusan Pemakaian Price Reference per material (Harga Terakhir atau Rata-rata)</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>FR-40: Price Reference per material: (a) History Pembelian — harga/unit (USD/kg) per bulan; (b) sistem menurunkan Harga Pembelian Terakhir (harga bulan terisi paling baru) dan Harga Pembelian Rata-rata (rata-rata bulan yang terisi); (c) per material, user memilih Keputusan Pemakaian Price Reference — "Harga Terakhir" atau rata-rata — dan pilihan itu dapat diubah; (d) Final Price Reference (USD) = harga sesuai pilihan; Final Price Reference (IDR/kg) = Final USD × Kurs.
+Sub-flow:
+1. Purchasing memilih material dan mengisi/mengubah History Pembelian (harga USD/kg per bulan).
+2. Sistem menurunkan Harga Pembelian Terakhir (bulan terisi paling baru) dan Harga Pembelian Rata-rata (rata-rata bulan terisi) dan menampilkannya.
+3. Purchasing memilih Keputusan Pemakaian Price Reference per material: 'Harga Terakhir' atau 'Rata-rata' (dapat diubah).
+4. Sistem menampilkan Final Price Reference (USD) sesuai pilihan dan Final Price Reference (IDR/kg) = Final USD × Kurs (master Kurs, UC-N07).
+Keputusan user 2026-10-07: master data dibangun dan diisi lewat UI sistem ini. User menetapkan seluruh UC ini kepada Purchasing, termasuk pilihan 'Harga Terakhir' vs 'Rata-rata' per material (user 2026-10-07; open question 10).</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>History Pembelian, Harga Terakhir, Harga Rata-rata, Final Price Reference USD dan IDR/kg per material tersimpan dan tampil</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>history_purchase, price_reference_header, price_reference_detail, material, master_kurs</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>UC-N09</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Kelola BOM Produk</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Produk; Varian Thickness (dipilih dari Master Material); material per varian</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>FR-41: BOM Produk: satu produk punya satu atau lebih varian BOM, dibedakan oleh ketebalan material (Varian Thickness diambil dari Master Material). Setiap varian punya No. Uniq ID sendiri (mis. Type 001.1, Type 001.2), Latest Update, dan Update By; aksi View, Edit, Delete. Satu produk boleh memakai beberapa varian material sekaligus.
+Sub-flow:
+1. Engineering membuka daftar BOM per produk.
+2. Engineering menambah varian BOM untuk produk: memilih material/ketebalan dari Master Material (satu produk boleh memakai beberapa varian sekaligus).
+3. Sistem membuat No. Uniq ID per varian (mis. Type 001.1, Type 001.2) dan mengisi Latest Update dan Update By.
+4. Engineering dapat View, Edit, atau Delete varian.
+Keputusan user 2026-10-07: master data dibangun dan diisi lewat UI sistem ini. Aktor Engineering sesuai kolom Updated By BOM pada sumber.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>BOM produk dengan varian, No. Uniq ID, Latest Update, dan Update By tersimpan dan tampil di daftar BOM</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>bom_header, bom_detail, product_lvl_4, material</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>UC-N10</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Kelola Flow Process &amp; Cycletime</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Costcentre/Area; Process Name; Machine; Cycletime (menit per meter); Man Power (jumlah orang)</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>FR-42: Flow Process &amp; Cycletime: per proses menyimpan Costcentre/Area, Process Name, Machine, Cycletime (menit per meter), Man Power (jumlah orang), dan Man Hour = Cycletime × Man Power ÷ 60 (jam per meter). Total Man Hour = jumlah Man Hour seluruh proses pada flow. Contoh sheet: Cutting Spandek, mesin 24 m/menit → cycletime 1 ÷ 24 = 0,0417 menit/meter, 1 man power → 0,000694 jam/meter. Flow dikunci per Product Category (Level 2), bukan per produk Level 4 (keputusan user 2026-10-07; open question 1).
+Sub-flow:
+1. Engineering membuka flow process (per Product Category / Level 2).
+2. Engineering menambah/mengubah/menghapus proses pada flow: mengisi Costcentre/Area, Process Name, Machine, Cycletime, dan Man Power.
+3. Sistem menghitung Man Hour per proses = Cycletime × Man Power ÷ 60 dan Total Man Hour flow, lalu menampilkannya.
+Keputusan user 2026-10-07: master data dibangun dan diisi lewat UI sistem ini. Kunci flow: Product Category (open question 1, resolved). Aktor ditetapkan user 2026-10-07 (open question 10).</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Flow process dengan Man Hour per proses dan Total Man Hour tersimpan dan tampil</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>flow_process_header, flow_process_detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>UC-N11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Kelola Man Power Rate</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Komponen Salary Direct Man Power; komponen BPJS (nilai rupiah input manual); komponen Biaya Lain-Lain; Faktor Indirect Labor; jam kerja per bulan (parameter); periode (bulan)</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>FR-43: Man Power Rate dihitung dari tiga kelompok komponen per bulan: Salary Direct Man Power (Gaji Pokok, Tunjangan Keluarga, Tunjangan Jabatan, THR, Cuti, Uang Makan, Transport), BPJS (Jaminan Kecelakaan Kerja 0,89%, Kematian 0,3%, Hari Tua 3,7%, Pensiun 2%, Kesehatan 4%) — nilai rupiah tiap komponen BPJS diinput manual (persentase hanya keterangan) — dan Biaya Lain-Lain (Seragam, Sepatu, Helm, Sarung Tangan, Masker — dihitung prorate per bulan). Lalu: Total Biaya Direct Labor/Bulan = jumlah tiga kelompok; Rate Direct Labor = pembulatan ke atas (Total ÷ jam kerja per bulan, parameter yang di contoh bernilai 173 jam; layar menampilkan keterangan konstanta yang dipakai); Rate Man Power (Rp/jam) = Rate Direct Labor × Faktor Indirect Labor. Contoh sheet: 6.551.982,55 → 37.873 → × 1,5 = 56.809,5 per jam. Komponen dapat ditambah/dihapus per kelompok (tombol Add/Delete di sheet).
+Sub-flow:
+1. Accounting membuka Man Power Rate per bulan.
+2. Accounting mengisi/mengubah komponen pada tiga kelompok (Salary Direct Man Power, BPJS, Biaya Lain-Lain) dan dapat menambah/menghapus komponen per kelompok (nilai rupiah BPJS diinput manual), serta mengisi Faktor Indirect Labor dan parameter jam kerja per bulan.
+3. Sistem menghitung Total Biaya Direct Labor/Bulan, Rate Direct Labor (dibulatkan ke atas, Total ÷ jam kerja per bulan), lalu menampilkan keterangan konstanta jam yang dipakai, dan Rate Man Power (Rp/jam), lalu menampilkannya.
+Keputusan user 2026-10-07: master data dibangun dan diisi lewat UI sistem ini. Perubahan rate tidak mengubah laporan produksi yang sudah dibuat (FR-49 / NFR-09). Open question 7 resolved: BPJS input manual; 173 jam menjadi parameter dengan keterangan ditampilkan. Aktor ditetapkan user 2026-10-07 (open question 10).</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Rate Man Power (Rp/jam) beserta rincian komponen tersimpan dan tampil</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>man_power_rate, man_power_rate_component</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>UC-N12</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Kelola Rate Bahan Pendukung Khusus &amp; FOH</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Product Category (atau Level 4); Rate Bahan Pendukung Khusus (Rp/meter); Rate FOH (Rp/meter)</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>FR-44: Rate Bahan Pendukung Khusus dan Rate FOH disimpan per Product Category dalam Rp/meter (contoh sheet: BONDECK 150 dan 400 — "contoh saja"). Kunci rate adalah Product Category (Level 2), bukan Level 4 (keputusan user 2026-10-07; open question 1).
+Sub-flow:
+1. Accounting membuka daftar rate Bahan Pendukung Khusus &amp; FOH.
+2. Accounting menambah/mengubah/menghapus rate per Product Category: Rate Bahan Pendukung Khusus dan Rate FOH dalam Rp/meter.
+3. Sistem menyimpan dan menampilkan kembali daftar rate.
+Keputusan user 2026-10-07: master data dibangun dan diisi lewat UI sistem ini. Perubahan rate tidak mengubah laporan produksi yang sudah dibuat (FR-49 / NFR-09). Kunci rate: Product Category (open question 1, resolved). Aktor ditetapkan user 2026-10-07 (open question 10).</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Rate Bahan Pendukung Khusus dan Rate FOH (Rp/meter) per kunci produk tersimpan dan tampil</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>rate_bahan_pendukung_foh</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>UC-N13</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Kelola General Rate</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Consumables (%); Scrap (%); Biaya Koordinasi (Rp/Kg); Other Cost (Sales &amp; Marketing, Transport, Finance &amp; Admin, Management Fee, Interest, Profit; masing-masing %); Negotiation Allowance (%)</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>FR-45: General Rate (berlaku semua produk): Consumables (% × Material Cost), Scrap (% × Material Cost), Biaya Koordinasi (Rp/Kg × Berat/Meter), Other Cost — Sales &amp; Marketing, Transport, Finance &amp; Admin, Management Fee, Interest, Profit (masing-masing % × HPP) — dan Negotiation Allowance (% × Bottom Price). Setiap baris punya jenis/satuan sendiri di master: Biaya Koordinasi = Rp/Kg, baris lainnya persentase. Contoh nilai di sheet: Consumables 5%, Scrap 2%, Koordinasi Rp200/Kg, Profit 5%, Negotiation Allowance 5%, lima Other Cost lain kosong (= 0). ERD menyediakan 6 slot Other Cost dan satu Negotiation Allowance.
+Sub-flow:
+1. Accounting membuka General Rate.
+2. Accounting mengisi/mengubah nilai Consumables, Scrap, Biaya Koordinasi, enam Other Cost, dan Negotiation Allowance (berlaku untuk semua produk).
+3. Sistem menyimpan dan menampilkan kembali nilai rate.
+Keputusan user 2026-10-07: master data dibangun dan diisi lewat UI sistem ini. Perubahan rate tidak mengubah laporan produksi yang sudah dibuat (FR-49 / NFR-09). Open question 11 resolved: tiap baris punya satuan/jenis sendiri (Koordinasi Rp/Kg, lainnya persentase). Aktor ditetapkan user 2026-10-07 (open question 10).</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>General Rate tersimpan dan tampil (satuan per baris: % atau Rp/Kg)</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>rate_generals</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>UC-N14</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Lihat Simulasi Costing &amp; Pricelist</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Accounting, Sales, Engineering</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Produk (dan varian BOM); Ukuran Produk (meter) diambil otomatis dari Panjang Master Produk</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>FR-46: Sistem menghitung, untuk setiap kombinasi Produk × varian BOM, dalam Rp/meter: Price Reference (Rp/Kg) = Final Price Reference IDR material varian tersebut (FR-40); Material Cost = Price Reference (Rp/Kg) × Berat/Meter material (FR-38); Man Power Cost = Total Man Hour (FR-42) × Rate Man Power (FR-43); Bahan Pendukung Khusus, FOH = rate FR-44; Consumables = % × Material Cost; Scrap = % × Material Cost; Biaya Koordinasi = Rp/Kg × Berat/Meter (FR-45); HPP = Material + Man Power + Bahan Pendukung + FOH + Consumables + Scrap + Koordinasi; Other Cost (6 komponen) = % × HPP; Bottom Price = HPP + seluruh Other Cost; Negotiation Allowance = % × Bottom Price; Price List/Meter = Bottom Price + Negotiation Allowance. Setiap nilai juga ditampilkan dalam Rp/Kg = nilai Rp/meter ÷ Berat/Meter. Berat per Pcs varian BOM = Berat/Meter material varian × Panjang produk (FR-37). Material Cost memakai Berat/Meter material utuh tanpa faktor lebar produk (dikonfirmasi user 2026-10-07, open question 2).
+FR-47: Output Simulasi Costing menampilkan satu baris per Produk × varian BOM (No. Uniq ID, Price Reference USD/Kg, Kurs, Rp/Kg, Berat/Meter, seluruh komponen FR-46 dalam Rp/meter dan Rp/Kg), ditambah Ukuran Produk (meter) yang diambil otomatis dari Panjang Master Produk (FR-37; keputusan user 2026-10-07), Pricelist Produk/Meter (= Ukuran × Price List/Meter) dan Pricelist Produk/Kg, sebagai pembanding terhadap "Pricelist HFG saat ini" (contoh 27.400 Rp/Meter; hanya contoh pembanding hasil hitung pricelist klien dengan konsep mock up, user 2026-10-07). Struktur yang sama dikonfirmasi ERD: Product Costing Header/Detail.
+Sub-flow:
+1. Aktor membuka layar Simulasi Costing; Ukuran Produk (meter) terisi otomatis dari Panjang Master Produk.
+2. Sistem menghitung untuk setiap kombinasi Produk × varian BOM seluruh komponen FR-46 (Rp/meter dan Rp/Kg) dari master: Price Reference, Berat/Meter, Man Hour, Rate Man Power, rate Bahan Pendukung/FOH, General Rate, dan Kurs.
+3. Sistem menampilkan satu baris per Produk × varian BOM: No. Uniq ID, Price Reference USD/Kg, Kurs, Rp/Kg, Berat/Meter, seluruh komponen FR-46, Pricelist Produk/Meter dan Pricelist Produk/Kg (pembanding 'Pricelist HFG saat ini').
+Tiga aktor (Accounting, Sales, Engineering) masing-masing memakai layar ini secara independen sebagai tampilan baca/simulasi (user menyatakan semuanya ikut memperkirakan harga dasar); tidak ada handoff di tengah alur sehingga tetap satu UC (admission test 1 dan 5). Open question 2 (Material Cost memakai Berat/Meter material utuh), 9 (Pricelist HFG saat ini = Rp/Meter, contoh), dan 5/6 (Scrap dari Rate Generals; jam laporan tidak dihitung) sudah resolved. Rumus tidak ditambah di luar FR-46.</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Tabel simulasi: satu baris per Produk × varian BOM dengan seluruh komponen biaya (Rp/meter dan Rp/Kg), Price List/Meter, serta Pricelist Produk/Meter dan /Kg</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>product_costing_header, product_costing_detail, material_cost, man_power_cost, bom_header, bom_detail, price_reference_header, flow_process_header, man_power_rate, rate_bahan_pendukung_foh, rate_generals, master_kurs, product_lvl_4</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1915,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="28.005" customWidth="1" style="1" min="1" max="1"/>
@@ -1506,12 +2014,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Unpack</t>
+          <t>Master Material</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Staf Gudang (master data, first pass)</t>
+          <t>Engineering (master data, first pass)</t>
         </is>
       </c>
       <c r="D5" s="3" t="b">
@@ -1611,7 +2119,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Admin Produksi (master data, first pass)</t>
+          <t>Engineering (master data, first pass)</t>
         </is>
       </c>
       <c r="D10" s="3" t="b">
@@ -1835,6 +2343,326 @@
         </is>
       </c>
       <c r="D21" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>master_kurs</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>history_purchase</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Purchasing</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>price_reference_header</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Purchasing</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>price_reference_detail</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Purchasing</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>bom_header</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>bom_detail</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>flow_process_header</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>flow_process_detail</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>man_power_rate</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>rate_bahan_pendukung_foh</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>rate_generals</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>product_costing_header</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>product_costing_detail</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>material_cost</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>man_power_cost</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>man_power_rate_component</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D37" t="b">
         <v>1</v>
       </c>
     </row>

--- a/specs/docs/workbook.xlsx
+++ b/specs/docs/workbook.xlsx
@@ -3,16 +3,17 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Modules" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="UC BPMN" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="UC Non-BPMN" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Entities" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Pages" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="171027" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -43,7 +44,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFd9d9d9"/>
+        <fgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,16 +58,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -74,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -85,7 +86,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -170,10 +170,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -211,71 +211,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -303,7 +303,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -326,11 +326,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -339,13 +339,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -355,7 +355,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -364,7 +364,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -373,7 +373,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -381,10 +381,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -455,14 +455,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="18.005" customWidth="1" style="1" min="1" max="1"/>
-    <col width="40.005" customWidth="1" style="1" min="2" max="2"/>
-    <col width="16.005" customWidth="1" style="1" min="3" max="3"/>
+    <col width="18" customWidth="1" style="1" min="1" max="1"/>
+    <col width="40" customWidth="1" style="1" min="2" max="2"/>
+    <col width="16" customWidth="1" style="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1" s="4">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" t="inlineStr">
         <is>
           <t>Modul</t>
@@ -623,7 +623,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Data master material (Berat/Meter dll.) untuk costing dan unpack</t>
+          <t>Data master material (Tebal Material, Lebar Coil, dll.) untuk costing dan unpack, serta Master Standard Material global (Standar Toleransi, Berat Jenis, Coating) untuk perhitungan Berat/Meter di BOM</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Master rate, BOM, flow process, price reference, kurs dan simulasi costing/pricelist</t>
+          <t>Master rate (Man Power Operator dan Borongan Helper, FOH, Bahan Pendukung, General Rate, Negotiation Allowance), BOM per varian tebal, flow process, kurs dan price reference, hasil costing sampai Bottom Price, serta alur Pricelist (approval Management) dan Product Catalog</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Accounting (first pass, belum dikonfirmasi klien)</t>
+          <t>Accounting / Costing (first pass, belum dikonfirmasi klien)</t>
         </is>
       </c>
     </row>
@@ -660,20 +660,21 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
+  <dimension ref="A1:I79"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="8.005000000000001" customWidth="1" style="4" min="1" max="1"/>
-    <col width="26.005" customWidth="1" style="4" min="2" max="2"/>
-    <col width="12.005" customWidth="1" style="4" min="3" max="3"/>
-    <col width="14.005" customWidth="1" style="4" min="4" max="4"/>
-    <col width="10.005" customWidth="1" style="4" min="5" max="5"/>
-    <col width="32.005" customWidth="1" style="4" min="6" max="6"/>
-    <col width="12.005" customWidth="1" style="4" min="7" max="7"/>
-    <col width="28.005" customWidth="1" style="4" min="8" max="8"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1" s="4">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Kode</t>
@@ -714,8 +715,13 @@
           <t>Entity/Objek Terkait</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="18.75" customHeight="1" s="4">
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Halaman</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>UC-01</t>
@@ -759,8 +765,13 @@
           <t>tr_unpack_coil_header, warehouse_pack, baby_coil, material, gudang_produksi_2</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1" s="4">
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>PG-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>UC-02</t>
@@ -801,8 +812,13 @@
           <t>laporan_ketidaksesuaian_material, baby_coil, material</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="18.75" customHeight="1" s="4">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>PG-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>UC-03</t>
@@ -843,8 +859,13 @@
           <t>material_coil, laporan_ketidaksesuaian_material</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1" s="4">
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>PG-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>UC-04</t>
@@ -886,8 +907,13 @@
           <t>production_report_items, baby_coil, product_lvl_4</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="18.75" customHeight="1" s="4">
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>PG-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>UC-05</t>
@@ -928,8 +954,13 @@
           <t>production_report_items, product_lvl_4</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="18.75" customHeight="1" s="4">
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>PG-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>UC-06</t>
@@ -970,8 +1001,13 @@
           <t>production_report_scraps</t>
         </is>
       </c>
-    </row>
-    <row r="8">
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>PG-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="154" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>UC-07</t>
@@ -1012,8 +1048,13 @@
           <t>production_report_scraps</t>
         </is>
       </c>
-    </row>
-    <row r="9">
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>PG-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="252" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>UC-08</t>
@@ -1056,8 +1097,13 @@
           <t>production_report_scraps, production_reports</t>
         </is>
       </c>
-    </row>
-    <row r="10">
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>PG-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="294" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>UC-09</t>
@@ -1100,8 +1146,13 @@
           <t>production_reports</t>
         </is>
       </c>
-    </row>
-    <row r="11">
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>PG-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="409.5" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>UC-10</t>
@@ -1150,8 +1201,13 @@
           <t>production_reports, stok_gudang_wip, production_plan, asset, employee</t>
         </is>
       </c>
-    </row>
-    <row r="12">
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>PG-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="409.5" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>UC-11</t>
@@ -1193,7 +1249,263 @@
           <t>jurnal_produksi, gl_interface, production_report_items, production_reports</t>
         </is>
       </c>
-    </row>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>PG-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="224" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>UC-12</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Tetapkan Rate Negotiation Allowance (Extra Margin) per Product Category</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Product Category; Rate Negotiation Allowance (Extra Margin, %)</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>FR-55 (user 2026-10-19). 1) Sales membuka daftar Rate Negotiation Allowance. 2) Sales menambah/mengubah/menghapus rate (%) per Product Category. 3) Sistem menyimpan, mengisi Latest Update dan Updated By, lalu menampilkan kembali daftar. Rate dipakai UC-13: Price List = Bottom Price + (Rate × Bottom Price); bukan lagi bagian Rate Generals. Dikerjakan berkala sesuai kebijakan. (Rev.1 UC-10; BPMN D05: 'Penetapan Rate Negotiation Allowance (Extra Margin)', lane Sales.)</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Rate Negotiation Allowance per Product Category tersimpan, siap dipakai untuk generate Pricelist</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>rate_negotiation_allowance</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>PG-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="409.5" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>UC-13</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Hitung Price List dan Ajukan Approval Pricelist</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Bottom Price per Produk × varian BOM (dari hasil costing UC-N14); Rate Negotiation Allowance per Product Category (UC-12); Draft Pricelist</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>FR-47, FR-57, FR-58. Prasyarat: hasil costing sampai Bottom Price (UC-N14) dan UC-12 tersedia. 1) Sales memilih Produk (dan varian BOM) dan menerima Bottom Price dari hasil costing. 2) Sistem menghitung Price List = Bottom Price + (Rate Negotiation Allowance kategori × Bottom Price), Rp/Meter dan Rp/Kg, serta Pricelist Produk/Meter (= Ukuran Produk × Price List/Meter) dan Pricelist Produk/Kg sebagai pembanding terhadap Pricelist HFG saat ini (contoh 27.400 Rp/Meter, hanya contoh). 3) Sistem menghasilkan Report Costing Detail/Produk. 4) Sales menyusun Draft Pricelist per Produk × varian BOM (status Draft) dan mengirimnya ke Management (Menunggu Approval). Bila Management menolak (UC-14), Sales menghitung ulang dengan alasan Reject terlihat lalu mengajukan lagi. (Rev.1 UC-16 dan UC-17; BPMN D05: User task 'Pengajuan Approval Pricelist', service task 'Perhitungan Price List' dan dokumen 'Report Costing Detail/Product' dilipat.) Revisi 2026-10-20 (FR-59): Draft Pricelist boleh disimpan, tetapi tidak boleh diajukan ke Management selama ada baris yang datanya belum lengkap (rate, Price Reference, Faktor Indirect Labor, dst.); sistem menyebut kekurangan dan menu untuk mengisinya.</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Price List per Produk × varian BOM dan Report Costing Detail/Produk tersedia; Draft Pricelist menunggu keputusan Management</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>pricelist_header, pricelist_detail, product_costing_detail, rate_negotiation_allowance</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>PG-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="252" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>UC-14</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Setujui / Tolak Pricelist</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Draft Pricelist yang dikirim; keputusan Approve atau Reject; alasan Reject (wajib bila Reject)</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>FR-58. Prasyarat: Draft Pricelist sudah dikirim (UC-13). 1) Management membuka Draft Pricelist yang menunggu approval. 2) Management memutuskan Approve atau Reject; alasan wajib bila Reject. 3) Sistem menyimpan keputusan, decided_by, decided_at, status, dan reject_reason. Status hanya Draft, Menunggu Approval, Approved, Rejected. Reject kembali ke UC-13; Approve memungkinkan UC-15. (Rev.1 UC-19; di BPMN D05 'Approval Pricelist' adalah gateway lane Management, dijadikan UC karena keputusannya dibuat manusia.)</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Pricelist berstatus Approved (lanjut ke UC-15) atau Rejected dengan alasan (kembali ke UC-13)</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>pricelist_header, pricelist_detail</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>PG-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="224" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>UC-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Rilis Product Catalog</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Pricelist berstatus Approved</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>FR-58. Prasyarat: pricelist Approved (UC-14). 1) Sales memilih Pricelist yang sudah Approved dan merilis Product Catalog. 2) Sistem menyimpan snapshot harga yang disetujui per Produk × varian BOM beserta released_by dan released_at (product_catalog_header/detail). 3) Product Catalog diteruskan ke proses Sales (di luar alur ini). Hanya pricelist Approved yang boleh dirilis; satu pricelist Approved boleh dirilis berkali-kali dan setiap rilis membuat Product Catalog (snapshot) baru (user 2026-10-20). (Rev.1 UC-18; BPMN D05 menggambarnya dengan ikon roda gigi, tetapi Use Case Rev.1 menyebut Sales yang merilis.)</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Product Catalog resmi dirilis dan tersimpan sebagai data; setiap rilis menghasilkan Product Catalog baru</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>product_catalog_header, product_catalog_detail, pricelist_header</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>PG-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1205,20 +1517,21 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
+  <dimension ref="A1:I79"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="10.005" customWidth="1" style="1" min="1" max="1"/>
-    <col width="26.005" customWidth="1" style="1" min="2" max="2"/>
-    <col width="12.005" customWidth="1" style="1" min="3" max="3"/>
-    <col width="14.005" customWidth="1" style="1" min="4" max="4"/>
-    <col width="10.005" customWidth="1" style="1" min="5" max="5"/>
-    <col width="32.005" customWidth="1" style="1" min="6" max="6"/>
-    <col width="12.005" customWidth="1" style="1" min="7" max="7"/>
-    <col width="28.005" customWidth="1" style="1" min="8" max="8"/>
+    <col width="10" customWidth="1" style="1" min="1" max="1"/>
+    <col width="26" customWidth="1" style="1" min="2" max="2"/>
+    <col width="12" customWidth="1" style="1" min="3" max="3"/>
+    <col width="14" customWidth="1" style="1" min="4" max="4"/>
+    <col width="10" customWidth="1" style="1" min="5" max="5"/>
+    <col width="32" customWidth="1" style="1" min="6" max="6"/>
+    <col width="12" customWidth="1" style="1" min="7" max="7"/>
+    <col width="28" customWidth="1" style="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1" s="4">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Kode</t>
@@ -1259,8 +1572,13 @@
           <t>Entity/Objek Terkait</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Halaman</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="322" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>UC-N01</t>
@@ -1302,8 +1620,13 @@
           <t>baby_coil, tr_unpack_coil_header, stok_gudang_wip, gudang_material_hold, material, production_report_materials</t>
         </is>
       </c>
-    </row>
-    <row r="3">
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>PG-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="280" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>UC-N02</t>
@@ -1345,8 +1668,13 @@
           <t>production_report_items, product_lvl_4, baby_coil</t>
         </is>
       </c>
-    </row>
-    <row r="4">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>PG-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="182" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>UC-N03</t>
@@ -1387,8 +1715,13 @@
           <t>warehouse_stock, baby_coil</t>
         </is>
       </c>
-    </row>
-    <row r="5">
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>PG-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="140" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>UC-N04</t>
@@ -1430,8 +1763,13 @@
           <t>warehouse_stock, baby_coil</t>
         </is>
       </c>
-    </row>
-    <row r="6">
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>PG-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="294" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>UC-N05</t>
@@ -1454,17 +1792,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Level 1 Product Type; Level 2 Product Category; Level 3 Product Jenis; Level 4 Product Master (nama produk); Lebar; Tebal; Panjang (meter)</t>
+          <t>Level 1 Product Type; Level 2 Product Category; Level 3 Product Jenis; Level 4 Product Master (nama produk); Lebar (kolom wide, mm); Tebal; Panjang (meter)</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>FR-37: Master Produk menyimpan hierarki 4 level (Level 1 Product Type, Level 2 Product Category, Level 3 Product Jenis, Level 4 Product Master/nama produk) dan Lebar (tetap per produk, karena satu lebar bisa memakai ketebalan material berbeda). Tebal dan Panjang (meter) tetap disimpan di Master Produk (keputusan user 2026-10-07, open question 3; menggantikan catatan sheet Ide E9–E11). Berat per Pcs tidak disimpan di produk: = Berat/Meter varian BOM × Panjang produk (FR-46). Contoh user: Produk 1 panjang 6 m; material A 1 kg/m → 6 kg, material B 1,3 kg/m → 7,8 kg.
-Sub-flow:
-1. Engineering membuka daftar Master Produk.
-2. Engineering menambah/mengubah/menghapus produk: mengisi hierarki 4 level, Lebar, Tebal, dan Panjang (meter).
-3. Sistem menyimpan dan menampilkan kembali daftar produk. (Berat per Pcs tidak diisi di sini — diturunkan dari Berat/Meter varian BOM × Panjang.)
-Keputusan user 2026-10-07: master data dibangun dan diisi lewat UI sistem ini. Open question 3 resolved: Tebal dan Panjang tetap ada di Master Produk; berat per pcs = Berat/Meter varian BOM × Panjang. Aktor ditetapkan user 2026-10-07 (open question 10).</t>
+          <t>FR-37. 1) Engineering membuka daftar Master Produk. 2) Engineering menambah/mengubah/menghapus produk: hierarki 4 level (Level 1 Product Type, Level 2 Product Category, Level 3 Product Jenis, Level 4 Product Master/nama produk), Lebar, Tebal, dan Panjang (meter). 3) Sistem menyimpan dan menampilkan kembali daftar. Berat per Pcs tidak disimpan di produk: = Berat/Meter varian BOM × Panjang (FR-46; contoh: panjang 6 m, material A 1 kg/m → 6 kg, material B 1,3 kg/m → 7,8 kg). Master data diisi lewat UI sistem ini (keputusan user 2026-10-07). (Rev.1 UC-01; BPMN D05: 'Develop New Product atau New Varian Product', lane Engineering.) Revisi 2026-10-20: Lebar produk memakai kolom yang sudah ada, wide (mm) (FR-64, keputusan D1); tidak ada kolom lebar baru. Produk yang sudah dipakai BOM tidak boleh dihapus (FR-61). Nama Level 4 disusun otomatis dan boleh ditimpa manual (FR-62). Contoh pilihan master: Baja Ringan &gt; CANAL C &gt; C75.70 B (FR-66).</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1477,8 +1810,13 @@
           <t>product_lvl_4</t>
         </is>
       </c>
-    </row>
-    <row r="7">
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>PG-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="210" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>UC-N06</t>
@@ -1501,22 +1839,17 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Metal Type; Slitted/Non Slit; Boron/Non Boron; Material Name; Width; Thickness; Berat/Meter (kg/m)</t>
+          <t>Metal Type; Slitted/Non Slit; Boron/Non Boron; Material Name; Width (Lebar Coil); Thickness (Tebal Material)</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>FR-38: Master Material menyimpan Metal Type, Slitted/Non Slit, Boron/Non Boron, Material Name, Width, Thickness, dan Berat/Meter (kg/m). Berat/Meter ditambahkan ke master karena dibutuhkan untuk konversi biaya dari Rp/Kg ke Rp/meter (catatan sheet Simulasi Program, I10), dan dipakai per varian BOM untuk menghitung Berat per Pcs. Contoh baris di sheet menulis Width 914 untuk material "…-1219-…"; itu salah ketik, nilai yang benar 1219 (input/2026-10-07-product-costing-jawaban/).
-Sub-flow:
-1. Engineering membuka daftar Master Material.
-2. Engineering menambah/mengubah/menghapus material dengan mengisi atribut di atas, termasuk Berat/Meter.
-3. Sistem menyimpan dan menampilkan kembali daftar material.
-Keputusan user 2026-10-07: master data dibangun dan diisi lewat UI sistem ini. Open question 8 resolved: Width yang benar 1219 (salah ketik pada contoh). Aktor ditetapkan user 2026-10-07 (open question 10).</t>
+          <t>FR-38 (revisi 2026-10-19). 1) Engineering membuka daftar Master Material. 2) Engineering menambah/mengubah/menghapus material: Metal Type, Slitted/Non Slit, Boron/Non Boron, Material Name, Width (Lebar Coil), Thickness (Tebal Material). 3) Sistem menyimpan dan menampilkan kembali daftar. Berat/Meter bukan atribut master: dihitung per varian BOM (FR-51, UC-N09). Width yang benar untuk contoh '…-1219-…' adalah 1219 (bukan 914). (Rev.1 UC-02.) Revisi 2026-10-20: material yang sudah dipakai BOM tidak boleh dihapus (FR-61); Material Name disusun otomatis dan boleh ditimpa manual (FR-62).</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Material (termasuk Berat/Meter) tersimpan dan tampil di daftar Master Material</t>
+          <t>Material (Tebal Material dan Lebar Coil) tersimpan dan tampil di daftar Master Material</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -1524,8 +1857,13 @@
           <t>material</t>
         </is>
       </c>
-    </row>
-    <row r="8">
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>PG-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="182" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>UC-N07</t>
@@ -1538,372 +1876,571 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Currency; Kurs</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>FR-39. 1) Finance membuka daftar Kurs. 2) Finance menambah/mengubah/menghapus Currency dan nilai Kurs. 3) Sistem mengisi Last Updated dan Updated By, lalu menampilkan kembali daftar. Kurs dipakai mengubah Price Reference USD ke Rupiah (UC-N08). Dipisah dari Price Reference mengikuti satu UC per User task BPMN. (Rev.1 UC-06 langkah 1; BPMN D05: 'Update Kurs', lane Finance.)</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Kurs tersimpan dengan Last Updated dan Updated By; tampil di daftar Kurs</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>master_kurs</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>PG-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="238" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>UC-N08</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Kelola Price Reference</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Material; History Pembelian (harga USD/kg per bulan, dibaca dari data pembelian); Price Reference USD/Kg</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>FR-52 (menggantikan FR-40 butir b–d). 1) Finance memilih material; sistem menampilkan History Pembelian (harga USD/kg per bulan) dan nilai Max-nya. 2) Finance memperbarui Price Reference USD/Kg per material dengan acuan Max (hanya Max yang dipakai; tidak ada pilihan terakhir/rata-rata). 3) Sistem menghitung Price Reference Rp/Kg = USD/Kg × Kurs terbaru (UC-N07) dan menampilkannya. (Rev.1 UC-06 langkah 2–3; BPMN D05: 'Update Price Reference USD/Kg' lane Finance, service task 'Price Reference Rp/Kg' dilipat.) Revisi 2026-10-20 (FR-65): tanggal Expired Price Reference dipilih lewat pemilih tanggal, bukan teks bebas.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Price Reference USD/Kg (acuan Max History Pembelian) dan Price Reference Rp/Kg per material tersimpan dan tampil</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>history_purchase, price_reference_header, price_reference_detail, material, master_kurs</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>PG-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="409.5" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>UC-N09</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Kelola BOM Produk</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Produk; Varian Tebal (material per varian, dipilih dari Master Material); Master Standard Material (global, dipakai otomatis)</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>FR-41, FR-51. Prasyarat: Master Produk (UC-N05), Master Material (UC-N06), Master Standard Material (UC-N15). 1) Engineering membuka daftar BOM per produk. 2) Engineering menambah varian BOM (Varian Tebal) untuk produk dengan memilih material dari Master Material. 3) Sistem menghitung Berat/Meter (kg/m) = ((Tebal Material − Standar Toleransi) × Lebar Coil × Standar Berat Jenis) + Coating dari Master Standard Material (global; satuan tidak ditampilkan, konversi dikalibrasi 0,14 mm × lebar 1219 × 7,85 ≈ 1,34 kg/m — FR-50) dan menyimpannya pada bom_detail. 4) Sistem membuat No. Uniq ID per varian (mis. Type 001.1) dan mengisi Latest Update dan Updated By. 5) Engineering dapat View, Edit, atau Delete varian. Satu produk boleh memakai beberapa material, tetapi tidak boleh memakai material yang sama dua kali (unik produk + material). (Rev.1 UC-04; BPMN D05: 'Develop BOM Produk berdasarkan Varian Tebal'.)</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>BOM produk per Varian Tebal dengan Berat/Meter terhitung, No. Uniq ID, Latest Update, dan Update By tersimpan dan tampil di daftar BOM</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>bom_header, bom_detail, product_lvl_4, material, master_standard_material</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>PG-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="350" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>UC-N10</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Kelola Flow Process &amp; Cycletime</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Costcentre/Area; Process Name; Machine; Cycletime (menit per meter); Man Power (jumlah orang)</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>FR-42. Prasyarat: Master Produk (UC-N05). 1) Engineering membuka flow process per Product Category (Level 2). 2) Engineering menambah/mengubah/menghapus proses: Costcentre/Area, Process Name, Machine, Cycletime (menit per meter), Man Power (jumlah orang). 3) Sistem menghitung Man Hour per proses = Cycletime × Man Power ÷ 60 (jam per meter) dan Total Man Hour flow, lalu menampilkannya. Contoh: Cutting Spandek, mesin 24 m/menit → cycletime 0,0417 menit/meter, 1 man power → 0,000694 jam/meter. Flow dikunci per Product Category, bukan Level 4 (keputusan user 2026-10-07). Total Man Hour dikalikan Rate 1/3 Operator pada Man Power Cost (FR-56, UC-N14). (Rev.1 UC-05; BPMN D05: 'Develop Flow Process &amp; Cycletime per Kategori Produk'.)</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Flow process dengan Man Hour per proses dan Total Man Hour per Kategori Produk tersimpan dan tampil</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>flow_process_header, flow_process_detail</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>PG-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="409.5" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>UC-N11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Kelola Man Power Rate (Operator)</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Costing</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Komponen Salary Direct Man Power Operator; komponen BPJS (nilai rupiah input manual); komponen Biaya Lain-Lain; jam kerja per bulan (parameter, contoh 173); porsi Operator (parameter, 1/3); periode (bulan)</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>FR-43, FR-53. 1) Costing membuka Man Power Rate per bulan. 2) Costing mengisi/mengubah komponen Operator pada tiga kelompok (boleh menambah/menghapus komponen): Salary Direct Man Power (Gaji Pokok, Tunjangan Keluarga, Tunjangan Jabatan, THR, Cuti, Uang Makan, Transport), BPJS (nilai rupiah tiap komponen diinput manual; persentase hanya keterangan), dan Biaya Lain-Lain (Seragam, Sepatu, Helm, Sarung Tangan, Masker, prorate per bulan), serta jam kerja per bulan (parameter, contoh 173) dan porsi Operator (parameter, 1/3). 3) Sistem menghitung Total Biaya Direct Labor/Bulan, Rate Direct Labor Operator = Total ÷ jam kerja, dan Rate 1/3 Operator (Rp/jam) = Rate Direct Labor Operator × 1/3, dibulatkan ke atas ke Rupiah penuh sesudah dikali 1/3 (user 2026-10-19; Operator dianggap hanya 1/3 bekerja langsung pada produk), lalu menampilkan keterangan konstanta. 4) Rate Borongan Helper ditetapkan terpisah di UC-N16 (halaman dan menu sendiri, user 2026-10-20). Faktor Indirect Labor ditetapkan terpisah di UC-N17 (master tersendiri, user 2026-10-20). 5) Man Power Cost dihitung di UC-N14: (Total Man Hour × Rate 1/3 Operator + Rate Borongan Helper Rp/Meter) × Faktor Indirect Labor (FR-56). Rincian gaji/BPJS kini hanya untuk Operator (satu Rate Man Power Rp/jam pada FR-43 lama digantikan). Perubahan rate tidak mengubah laporan produksi yang sudah dibuat (FR-49, NFR-09). (Rev.1 UC-07 bagian Man Power; BPMN D05: 'Penetapan Rate Man Hour', lane Costing (Rate).)</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Rate 1/3 Operator beserta rincian komponen tersimpan dan tampil</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>man_power_rate, man_power_rate_component</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>PG-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="322" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>UC-N12</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Kelola Rate Bahan Pendukung Khusus &amp; FOH</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Costing</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Product Category; Rate Bahan Pendukung Khusus (Rp/Kg); Rate FOH (Rp/Kg)</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>FR-44 (revisi), FR-53. 1) Costing membuka daftar rate Bahan Pendukung Khusus &amp; FOH. 2) Costing menambah/mengubah/menghapus rate per Product Category (Level 2): Rate Bahan Pendukung Khusus dan Rate FOH dalam Rp/Kg. 3) Sistem menyimpan dan menampilkan kembali daftar. Rp/Meter dihitung di Product Costing = Rate (Rp/Kg) × Berat/Meter varian BOM (FR-56). Nilai contoh lama (150/400 per meter) tidak berlaku. Perubahan rate tidak mengubah laporan produksi yang sudah dibuat (FR-49). (Rev.1 UC-07 bagian FOH dan Bahan Pendukung Khusus; BPMN D05: 'Penetapan Rate FOH per Kategori Produk' dan 'Penetapan Rate Bahan Pendukung Khusus per Kategori Produk'.)</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Rate Bahan Pendukung Khusus dan Rate FOH (Rp/Kg) per Product Category tersimpan dan tampil</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>rate_bahan_pendukung_foh</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>PG-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="392" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>UC-N13</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Kelola General Rate</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Costing</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Rate Consumables (Rp/Kg); Rate Scrap (% dari Material Cost); Rate Biaya Koordinasi (Rp/Kg); Rate Other Cost (Sales &amp; Marketing, Transport, Finance &amp; Admin, Management Fee, Interest, Profit; masing-masing % × HPP)</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>FR-45 (revisi), FR-54, FR-55. 1) Costing membuka General Rate. 2) Costing mengisi/mengubah Rate Consumables (Rp/Kg; Rp/Meter = Rate × Berat/Meter), Rate Scrap (% × Material Cost), Rate Biaya Koordinasi (Rp/Kg; Rp/Meter = Rate × Berat/Meter), dan enam Rate Other Cost — Sales &amp; Marketing, Transport, Finance &amp; Admin, Management Fee, Interest, Profit (masing-masing % × HPP); berlaku semua produk. 3) Sistem menyimpan dan menampilkan kembali nilai rate. Daftar Other Cost = enam elemen UC-09 (user 2026-10-19); daftar empat elemen di sheet Istilah/BPMN usang. Setiap baris punya jenis/satuan sendiri. Negotiation Allowance bukan bagian General Rate (UC-12). Perubahan rate tidak mengubah laporan produksi yang sudah dibuat (FR-49). (Rev.1 UC-08 dan UC-09, digabung karena satu aktor, satu layar, satu sitting.)</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>General Rate (Consumables, Scrap, Biaya Koordinasi, enam Other Cost) tersimpan dan tampil (satuan per baris: % atau Rp/Kg)</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>rate_generals</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>PG-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="409.5" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>UC-N14</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Lihat Hasil Costing per Produk × Varian BOM (Material Cost sampai Bottom Price)</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
           <t>Accounting</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Product Costing</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Currency; Kurs</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>FR-39: Master Kurs menyimpan Currency, Kurs, Last Updated, dan Updated By. Kurs dipakai mengubah Price Reference dari USD ke Rupiah.
-Sub-flow:
-1. Accounting membuka daftar Kurs.
-2. Accounting menambah/mengubah/menghapus Currency dan nilai Kurs.
-3. Sistem mengisi Last Updated dan Updated By, lalu menampilkan kembali daftar.
-Keputusan user 2026-10-07: master data dibangun dan diisi lewat UI sistem ini. Kurs dipakai oleh UC-N08 untuk mengubah Price Reference USD ke Rupiah. Aktor Accounting sesuai kolom Updated By pada sumber.</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Kurs tersimpan dengan Last Updated dan Updated By; tampil di daftar Kurs</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>master_kurs</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>UC-N08</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Kelola Price Reference</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Purchasing</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Produk (dan varian BOM); Ukuran Produk (meter) diambil otomatis dari Panjang Master Produk</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>FR-46, FR-47 (kolom pricelist pindah ke UC-13), FR-56, FR-57. Prasyarat: BOM (UC-N09), Price Reference (UC-N08), Flow Process (UC-N10), dan rate (UC-N11, N12, N13) tersedia. BM = Berat/Meter varian BOM; semua nilai dalam Rp/Meter dan Rp/Kg. 1) Accounting memilih Produk (dan varian BOM); sistem mengambil BOM, BM, Price Reference Rp/Kg, Total Man Hour, rate per Product Category, dan General Rate. 2) Material Cost: Rp/Kg = Price Reference Rp/Kg; Rp/Meter = Price Reference × BM. 3) Biaya Proses: Man Power Rp/Meter = (Total Man Hour × Rate 1/3 Operator + Rate Borongan Helper Rp/Meter) × Faktor Indirect Labor; FOH dan Bahan Pendukung Khusus Rp/Meter = Rate (Rp/Kg) × BM; Rp/Kg = Rp/Meter ÷ BM; Biaya Proses = jumlah ketiganya. 4) Manufacturing Support: Consumables dan Biaya Koordinasi Rp/Meter = Rate (Rp/Kg) × BM; Scrap = Rate Scrap × Material Cost (Rp/Meter dan Rp/Kg masing-masing); jumlah ketiganya. 5) HPP = Material Cost + Biaya Proses + Manufacturing Support. 6) Other Cost tiap enam elemen = Rate × HPP; Bottom Price = HPP + Σ Other Cost. 7) Sistem menampilkan satu baris per Produk × varian BOM: No. Uniq ID, Price Reference USD/Kg, Kurs, Rp/Kg, BM, Ukuran Produk (meter, dari Panjang Master Produk), dan seluruh komponen sampai Bottom Price. Material Cost memakai Berat/Meter material utuh tanpa faktor lebar (user 2026-10-07). Hasil menjadi input UC-13; Sales dan Engineering boleh melihat sebagai tampilan baca (NFR-13). (Rev.1 UC-11 s.d. UC-15: semuanya Service task lane Accounting, dijalankan otomatis, dilipat sebagai sub-flow satu UC. Butir 1.1 UC-12 Rev.1 'Rate × Berat/Meter' dan judul langkah 4 UC-13 Rev.1 'Biaya Proses' salah tulis, user 2026-10-19.) Revisi 2026-10-20: data yang belum lengkap ditandai dan disebutkan kekurangannya (FR-59); semua rupiah 2 desimal, hanya Rate 1/3 Operator dibulatkan ke atas (FR-60); filter Range Date berupa pemilih tanggal (FR-65). Angka acuan uji: NFR-11.</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Tabel hasil costing: satu baris per Produk × varian BOM dengan Material Cost, Biaya Proses, Manufacturing Support, HPP, Other Cost, dan Bottom Price (Rp/Meter dan Rp/Kg)</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>product_costing_header, product_costing_detail, material_cost, man_power_cost, bom_header, bom_detail, price_reference_header, price_reference_detail, flow_process_header, man_power_rate, rate_borongan_helper, rate_bahan_pendukung_foh, rate_generals, master_kurs, product_lvl_4</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>PG-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="280" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>UC-N15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Tetapkan Master Standard Material</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Master Material</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Standar Toleransi; Standar Berat Jenis Material Baja; Coating</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>FR-50. 1) Engineering membuka Master Standard Material. 2) Engineering mengisi/mengubah Standar Toleransi, Standar Berat Jenis Material Baja, dan Coating. 3) Sistem menyimpan, mengisi Latest Update dan Updated By, dan menampilkan nilainya. Berlaku global — satu set nilai untuk semua material (user 2026-10-19). Satuan tidak ditampilkan karena klien tidak menginformasikannya; angka dipakai apa adanya dan konversi dikalibrasi 0,14 mm × lebar 1219 × 7,85 ≈ 1,34 kg/m. Dipakai formula Berat/Meter di BOM (FR-51, UC-N09). Tidak punya task di BPMN D05 (dipakai oleh 'Develop BOM Produk'), maka masuk sheet ini. (Rev.1 UC-03.) Revisi 2026-10-20 (FR-63): satu baris global, presisi DECIMAL(14,6), perubahan nilai dicatat before/after.</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Master Standard Material (global) tersimpan dan tersedia untuk perhitungan Berat/Meter di BOM</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>master_standard_material</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>PG-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="409.5" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>UC-N16</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Kelola Rate Borongan Helper</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Costing</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Product Costing</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Material; Harga pembelian per bulan (USD/kg); Keputusan Pemakaian Price Reference per material (Harga Terakhir atau Rata-rata)</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>FR-40: Price Reference per material: (a) History Pembelian — harga/unit (USD/kg) per bulan; (b) sistem menurunkan Harga Pembelian Terakhir (harga bulan terisi paling baru) dan Harga Pembelian Rata-rata (rata-rata bulan yang terisi); (c) per material, user memilih Keputusan Pemakaian Price Reference — "Harga Terakhir" atau rata-rata — dan pilihan itu dapat diubah; (d) Final Price Reference (USD) = harga sesuai pilihan; Final Price Reference (IDR/kg) = Final USD × Kurs.
-Sub-flow:
-1. Purchasing memilih material dan mengisi/mengubah History Pembelian (harga USD/kg per bulan).
-2. Sistem menurunkan Harga Pembelian Terakhir (bulan terisi paling baru) dan Harga Pembelian Rata-rata (rata-rata bulan terisi) dan menampilkannya.
-3. Purchasing memilih Keputusan Pemakaian Price Reference per material: 'Harga Terakhir' atau 'Rata-rata' (dapat diubah).
-4. Sistem menampilkan Final Price Reference (USD) sesuai pilihan dan Final Price Reference (IDR/kg) = Final USD × Kurs (master Kurs, UC-N07).
-Keputusan user 2026-10-07: master data dibangun dan diisi lewat UI sistem ini. User menetapkan seluruh UC ini kepada Purchasing, termasuk pilihan 'Harga Terakhir' vs 'Rata-rata' per material (user 2026-10-07; open question 10).</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>History Pembelian, Harga Terakhir, Harga Rata-rata, Final Price Reference USD dan IDR/kg per material tersimpan dan tampil</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>history_purchase, price_reference_header, price_reference_detail, material, master_kurs</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>UC-N09</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Kelola BOM Produk</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Product Category; Rate Borongan Helper (Rp/Meter)</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>FR-53. 1) Costing membuka daftar Rate Borongan Helper. 2) Costing menambah/mengubah/menghapus rate per Product Category (Level 2) dalam Rp/Meter (satu-satunya satuan; tidak ada Rp/Pcs dan tidak ada konversi dengan Panjang Produk, user 2026-10-20). 3) Rate Borongan Helper Rp/Meter dipakai UC-N14 pada Man Power Cost: (Total Man Hour × Rate 1/3 Operator + Rate Borongan Helper Rp/Meter) × Faktor Indirect Labor (FR-56). Perubahan rate tidak mengubah laporan produksi yang sudah dibuat (FR-49, NFR-09). Dipisah dari UC-N11 menjadi halaman dan menu sendiri (user 2026-10-20). (Rev.1 UC-07 bagian Man Power: Rate Borongan Helper per Product Category.)</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Rate Borongan Helper per Product Category (Rp/Meter) tersimpan dan tampil</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>rate_borongan_helper</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>PG-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="409.5" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>UC-N17</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Kelola Faktor Indirect Labor</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Costing</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Product Costing</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Produk; Varian Thickness (dipilih dari Master Material); material per varian</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>FR-41: BOM Produk: satu produk punya satu atau lebih varian BOM, dibedakan oleh ketebalan material (Varian Thickness diambil dari Master Material). Setiap varian punya No. Uniq ID sendiri (mis. Type 001.1, Type 001.2), Latest Update, dan Update By; aksi View, Edit, Delete. Satu produk boleh memakai beberapa varian material sekaligus.
-Sub-flow:
-1. Engineering membuka daftar BOM per produk.
-2. Engineering menambah varian BOM untuk produk: memilih material/ketebalan dari Master Material (satu produk boleh memakai beberapa varian sekaligus).
-3. Sistem membuat No. Uniq ID per varian (mis. Type 001.1, Type 001.2) dan mengisi Latest Update dan Update By.
-4. Engineering dapat View, Edit, atau Delete varian.
-Keputusan user 2026-10-07: master data dibangun dan diisi lewat UI sistem ini. Aktor Engineering sesuai kolom Updated By BOM pada sumber.</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>BOM produk dengan varian, No. Uniq ID, Latest Update, dan Update By tersimpan dan tampil di daftar BOM</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>bom_header, bom_detail, product_lvl_4, material</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>UC-N10</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Kelola Flow Process &amp; Cycletime</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Product Costing</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Costcentre/Area; Process Name; Machine; Cycletime (menit per meter); Man Power (jumlah orang)</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>FR-42: Flow Process &amp; Cycletime: per proses menyimpan Costcentre/Area, Process Name, Machine, Cycletime (menit per meter), Man Power (jumlah orang), dan Man Hour = Cycletime × Man Power ÷ 60 (jam per meter). Total Man Hour = jumlah Man Hour seluruh proses pada flow. Contoh sheet: Cutting Spandek, mesin 24 m/menit → cycletime 1 ÷ 24 = 0,0417 menit/meter, 1 man power → 0,000694 jam/meter. Flow dikunci per Product Category (Level 2), bukan per produk Level 4 (keputusan user 2026-10-07; open question 1).
-Sub-flow:
-1. Engineering membuka flow process (per Product Category / Level 2).
-2. Engineering menambah/mengubah/menghapus proses pada flow: mengisi Costcentre/Area, Process Name, Machine, Cycletime, dan Man Power.
-3. Sistem menghitung Man Hour per proses = Cycletime × Man Power ÷ 60 dan Total Man Hour flow, lalu menampilkannya.
-Keputusan user 2026-10-07: master data dibangun dan diisi lewat UI sistem ini. Kunci flow: Product Category (open question 1, resolved). Aktor ditetapkan user 2026-10-07 (open question 10).</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Flow process dengan Man Hour per proses dan Total Man Hour tersimpan dan tampil</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>flow_process_header, flow_process_detail</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>UC-N11</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Kelola Man Power Rate</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Accounting</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Product Costing</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Komponen Salary Direct Man Power; komponen BPJS (nilai rupiah input manual); komponen Biaya Lain-Lain; Faktor Indirect Labor; jam kerja per bulan (parameter); periode (bulan)</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>FR-43: Man Power Rate dihitung dari tiga kelompok komponen per bulan: Salary Direct Man Power (Gaji Pokok, Tunjangan Keluarga, Tunjangan Jabatan, THR, Cuti, Uang Makan, Transport), BPJS (Jaminan Kecelakaan Kerja 0,89%, Kematian 0,3%, Hari Tua 3,7%, Pensiun 2%, Kesehatan 4%) — nilai rupiah tiap komponen BPJS diinput manual (persentase hanya keterangan) — dan Biaya Lain-Lain (Seragam, Sepatu, Helm, Sarung Tangan, Masker — dihitung prorate per bulan). Lalu: Total Biaya Direct Labor/Bulan = jumlah tiga kelompok; Rate Direct Labor = pembulatan ke atas (Total ÷ jam kerja per bulan, parameter yang di contoh bernilai 173 jam; layar menampilkan keterangan konstanta yang dipakai); Rate Man Power (Rp/jam) = Rate Direct Labor × Faktor Indirect Labor. Contoh sheet: 6.551.982,55 → 37.873 → × 1,5 = 56.809,5 per jam. Komponen dapat ditambah/dihapus per kelompok (tombol Add/Delete di sheet).
-Sub-flow:
-1. Accounting membuka Man Power Rate per bulan.
-2. Accounting mengisi/mengubah komponen pada tiga kelompok (Salary Direct Man Power, BPJS, Biaya Lain-Lain) dan dapat menambah/menghapus komponen per kelompok (nilai rupiah BPJS diinput manual), serta mengisi Faktor Indirect Labor dan parameter jam kerja per bulan.
-3. Sistem menghitung Total Biaya Direct Labor/Bulan, Rate Direct Labor (dibulatkan ke atas, Total ÷ jam kerja per bulan), lalu menampilkan keterangan konstanta jam yang dipakai, dan Rate Man Power (Rp/jam), lalu menampilkannya.
-Keputusan user 2026-10-07: master data dibangun dan diisi lewat UI sistem ini. Perubahan rate tidak mengubah laporan produksi yang sudah dibuat (FR-49 / NFR-09). Open question 7 resolved: BPJS input manual; 173 jam menjadi parameter dengan keterangan ditampilkan. Aktor ditetapkan user 2026-10-07 (open question 10).</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Rate Man Power (Rp/jam) beserta rincian komponen tersimpan dan tampil</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>man_power_rate, man_power_rate_component</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>UC-N12</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Kelola Rate Bahan Pendukung Khusus &amp; FOH</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Accounting</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Product Costing</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Product Category (atau Level 4); Rate Bahan Pendukung Khusus (Rp/meter); Rate FOH (Rp/meter)</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>FR-44: Rate Bahan Pendukung Khusus dan Rate FOH disimpan per Product Category dalam Rp/meter (contoh sheet: BONDECK 150 dan 400 — "contoh saja"). Kunci rate adalah Product Category (Level 2), bukan Level 4 (keputusan user 2026-10-07; open question 1).
-Sub-flow:
-1. Accounting membuka daftar rate Bahan Pendukung Khusus &amp; FOH.
-2. Accounting menambah/mengubah/menghapus rate per Product Category: Rate Bahan Pendukung Khusus dan Rate FOH dalam Rp/meter.
-3. Sistem menyimpan dan menampilkan kembali daftar rate.
-Keputusan user 2026-10-07: master data dibangun dan diisi lewat UI sistem ini. Perubahan rate tidak mengubah laporan produksi yang sudah dibuat (FR-49 / NFR-09). Kunci rate: Product Category (open question 1, resolved). Aktor ditetapkan user 2026-10-07 (open question 10).</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Rate Bahan Pendukung Khusus dan Rate FOH (Rp/meter) per kunci produk tersimpan dan tampil</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>rate_bahan_pendukung_foh</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>UC-N13</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Kelola General Rate</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Accounting</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Product Costing</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Consumables (%); Scrap (%); Biaya Koordinasi (Rp/Kg); Other Cost (Sales &amp; Marketing, Transport, Finance &amp; Admin, Management Fee, Interest, Profit; masing-masing %); Negotiation Allowance (%)</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>FR-45: General Rate (berlaku semua produk): Consumables (% × Material Cost), Scrap (% × Material Cost), Biaya Koordinasi (Rp/Kg × Berat/Meter), Other Cost — Sales &amp; Marketing, Transport, Finance &amp; Admin, Management Fee, Interest, Profit (masing-masing % × HPP) — dan Negotiation Allowance (% × Bottom Price). Setiap baris punya jenis/satuan sendiri di master: Biaya Koordinasi = Rp/Kg, baris lainnya persentase. Contoh nilai di sheet: Consumables 5%, Scrap 2%, Koordinasi Rp200/Kg, Profit 5%, Negotiation Allowance 5%, lima Other Cost lain kosong (= 0). ERD menyediakan 6 slot Other Cost dan satu Negotiation Allowance.
-Sub-flow:
-1. Accounting membuka General Rate.
-2. Accounting mengisi/mengubah nilai Consumables, Scrap, Biaya Koordinasi, enam Other Cost, dan Negotiation Allowance (berlaku untuk semua produk).
-3. Sistem menyimpan dan menampilkan kembali nilai rate.
-Keputusan user 2026-10-07: master data dibangun dan diisi lewat UI sistem ini. Perubahan rate tidak mengubah laporan produksi yang sudah dibuat (FR-49 / NFR-09). Open question 11 resolved: tiap baris punya satuan/jenis sendiri (Koordinasi Rp/Kg, lainnya persentase). Aktor ditetapkan user 2026-10-07 (open question 10).</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>General Rate tersimpan dan tampil (satuan per baris: % atau Rp/Kg)</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>rate_generals</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>UC-N14</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Lihat Simulasi Costing &amp; Pricelist</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Accounting, Sales, Engineering</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Product Costing</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Produk (dan varian BOM); Ukuran Produk (meter) diambil otomatis dari Panjang Master Produk</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>FR-46: Sistem menghitung, untuk setiap kombinasi Produk × varian BOM, dalam Rp/meter: Price Reference (Rp/Kg) = Final Price Reference IDR material varian tersebut (FR-40); Material Cost = Price Reference (Rp/Kg) × Berat/Meter material (FR-38); Man Power Cost = Total Man Hour (FR-42) × Rate Man Power (FR-43); Bahan Pendukung Khusus, FOH = rate FR-44; Consumables = % × Material Cost; Scrap = % × Material Cost; Biaya Koordinasi = Rp/Kg × Berat/Meter (FR-45); HPP = Material + Man Power + Bahan Pendukung + FOH + Consumables + Scrap + Koordinasi; Other Cost (6 komponen) = % × HPP; Bottom Price = HPP + seluruh Other Cost; Negotiation Allowance = % × Bottom Price; Price List/Meter = Bottom Price + Negotiation Allowance. Setiap nilai juga ditampilkan dalam Rp/Kg = nilai Rp/meter ÷ Berat/Meter. Berat per Pcs varian BOM = Berat/Meter material varian × Panjang produk (FR-37). Material Cost memakai Berat/Meter material utuh tanpa faktor lebar produk (dikonfirmasi user 2026-10-07, open question 2).
-FR-47: Output Simulasi Costing menampilkan satu baris per Produk × varian BOM (No. Uniq ID, Price Reference USD/Kg, Kurs, Rp/Kg, Berat/Meter, seluruh komponen FR-46 dalam Rp/meter dan Rp/Kg), ditambah Ukuran Produk (meter) yang diambil otomatis dari Panjang Master Produk (FR-37; keputusan user 2026-10-07), Pricelist Produk/Meter (= Ukuran × Price List/Meter) dan Pricelist Produk/Kg, sebagai pembanding terhadap "Pricelist HFG saat ini" (contoh 27.400 Rp/Meter; hanya contoh pembanding hasil hitung pricelist klien dengan konsep mock up, user 2026-10-07). Struktur yang sama dikonfirmasi ERD: Product Costing Header/Detail.
-Sub-flow:
-1. Aktor membuka layar Simulasi Costing; Ukuran Produk (meter) terisi otomatis dari Panjang Master Produk.
-2. Sistem menghitung untuk setiap kombinasi Produk × varian BOM seluruh komponen FR-46 (Rp/meter dan Rp/Kg) dari master: Price Reference, Berat/Meter, Man Hour, Rate Man Power, rate Bahan Pendukung/FOH, General Rate, dan Kurs.
-3. Sistem menampilkan satu baris per Produk × varian BOM: No. Uniq ID, Price Reference USD/Kg, Kurs, Rp/Kg, Berat/Meter, seluruh komponen FR-46, Pricelist Produk/Meter dan Pricelist Produk/Kg (pembanding 'Pricelist HFG saat ini').
-Tiga aktor (Accounting, Sales, Engineering) masing-masing memakai layar ini secara independen sebagai tampilan baca/simulasi (user menyatakan semuanya ikut memperkirakan harga dasar); tidak ada handoff di tengah alur sehingga tetap satu UC (admission test 1 dan 5). Open question 2 (Material Cost memakai Berat/Meter material utuh), 9 (Pricelist HFG saat ini = Rp/Meter, contoh), dan 5/6 (Scrap dari Rate Generals; jam laporan tidak dihitung) sudah resolved. Rumus tidak ditambah di luar FR-46.</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Tabel simulasi: satu baris per Produk × varian BOM dengan seluruh komponen biaya (Rp/meter dan Rp/Kg), Price List/Meter, serta Pricelist Produk/Meter dan /Kg</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>product_costing_header, product_costing_detail, material_cost, man_power_cost, bom_header, bom_detail, price_reference_header, flow_process_header, man_power_rate, rate_bahan_pendukung_foh, rate_generals, master_kurs, product_lvl_4</t>
-        </is>
-      </c>
-    </row>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Faktor Indirect Labor (nilai, global)</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>FR-53. 1) Costing membuka master Faktor Indirect Labor. 2) Costing mengubah nilai faktor (satu nilai global; wajib lebih besar dari 0; sistem menampilkan Last Update dan Updated By). 3) Faktor dipakai UC-N14 pada Man Power Cost: (Total Man Hour × Rate 1/3 Operator + Rate Borongan Helper Rp/Meter) × Faktor Indirect Labor (FR-56). 4) Perubahan tidak mengubah Pricelist yang sudah diajukan (snapshot) dan laporan produksi yang sudah dibuat (FR-49, NFR-09). Dijadikan master tersendiri karena nilainya dapat berubah (user 2026-10-20); cakupan global: tidak per Product Category dan hanya pengali pada Man Power Cost (dikonfirmasi user 2026-10-20). (Rev.1 UC-07 bagian Man Power: Faktor Indirect Labor.)</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Faktor Indirect Labor tersimpan dengan Last Update dan Updated By, dan tampil</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>faktor_indirect_labor</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>PG-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1915,16 +2452,16 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
+  <dimension ref="A1:D45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="28.005" customWidth="1" style="1" min="1" max="1"/>
-    <col width="16.005" customWidth="1" style="1" min="2" max="2"/>
-    <col width="8.005000000000001" customWidth="1" style="5" min="3" max="3"/>
-    <col width="8.005000000000001" customWidth="1" style="4" min="4" max="4"/>
+    <col width="28" customWidth="1" style="1" min="1" max="1"/>
+    <col width="16" customWidth="1" style="1" min="2" max="2"/>
+    <col width="8" customWidth="1" style="4" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1" s="4">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Entity yang dibutuhkan</t>
@@ -1946,7 +2483,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>tr_unpack_coil_header</t>
@@ -1966,7 +2503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="28" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>warehouse_pack</t>
@@ -1986,7 +2523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>baby_coil</t>
@@ -2006,7 +2543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="84" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>material</t>
@@ -2026,7 +2563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="84" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>gudang_produksi_2</t>
@@ -2046,7 +2583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="28" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>laporan_ketidaksesuaian_material</t>
@@ -2086,27 +2623,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="42" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>warehouse_stock</t>
+          <t>production_report_items</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Gudang Produksi 2</t>
+          <t>Report Produksi</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Staf Gudang (master data, first pass)</t>
+          <t>Admin Produksi</t>
         </is>
       </c>
       <c r="D9" s="3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="84" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>product_lvl_4</t>
@@ -2126,10 +2663,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="42" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>stok_gudang_wip</t>
+          <t>production_report_scraps</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2146,140 +2683,140 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="42" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>jurnal_produksi</t>
+          <t>production_reports</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Report HPP</t>
+          <t>Report Produksi</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Admin Produksi</t>
         </is>
       </c>
       <c r="D12" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="42" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>gl_interface</t>
+          <t>stok_gudang_wip</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Report HPP</t>
+          <t>Report Produksi</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Admin Produksi</t>
         </is>
       </c>
       <c r="D13" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="98" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>gudang_material_hold</t>
+          <t>production_plan</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Gudang Produksi 2</t>
+          <t>Production Plan (Eksternal)</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Staf Gudang (master data, first pass)</t>
+          <t>Production Planning (eksternal, read-only)</t>
         </is>
       </c>
       <c r="D14" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="98" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>employee</t>
+          <t>asset</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Master Employee</t>
+          <t>Master Asset</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Admin Produksi (master data, first pass)</t>
+          <t>Staf Produksi (master data, first pass)</t>
         </is>
       </c>
       <c r="D15" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="98" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>employee</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Master Asset</t>
+          <t>Master Employee</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Staf Produksi (master data, first pass)</t>
+          <t>Admin Produksi (master data, first pass)</t>
         </is>
       </c>
       <c r="D16" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="28" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>production_plan</t>
+          <t>jurnal_produksi</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Production Plan (Eksternal)</t>
+          <t>Report HPP</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Production Planning (eksternal, read-only)</t>
+          <t>Accounting</t>
         </is>
       </c>
       <c r="D17" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="28" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>production_reports</t>
+          <t>gl_interface</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Report Produksi</t>
+          <t>Report HPP</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Admin Produksi</t>
+          <t>Accounting</t>
         </is>
       </c>
       <c r="D18" s="3" t="b">
@@ -2289,17 +2826,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>production_report_materials</t>
+          <t>rate_negotiation_allowance</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Report Produksi</t>
+          <t>Product Costing</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Admin Produksi</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D19" s="3" t="b">
@@ -2309,17 +2846,17 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>production_report_items</t>
+          <t>pricelist_header</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Report Produksi</t>
+          <t>Product Costing</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Admin Produksi</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D20" s="3" t="b">
@@ -2329,27 +2866,27 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>production_report_scraps</t>
+          <t>pricelist_detail</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Report Produksi</t>
+          <t>Product Costing</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Admin Produksi</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D21" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="28" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>master_kurs</t>
+          <t>product_costing_detail</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2369,7 +2906,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>history_purchase</t>
+          <t>product_catalog_header</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -2379,7 +2916,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Purchasing</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D23" s="3" t="b">
@@ -2389,7 +2926,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>price_reference_header</t>
+          <t>product_catalog_detail</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2399,77 +2936,77 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Purchasing</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D24" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="84" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>price_reference_detail</t>
+          <t>gudang_material_hold</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Product Costing</t>
+          <t>Gudang Produksi 2</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Purchasing</t>
+          <t>Staf Gudang (master data, first pass)</t>
         </is>
       </c>
       <c r="D25" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="42" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>bom_header</t>
+          <t>production_report_materials</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Product Costing</t>
+          <t>Report Produksi</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Admin Produksi</t>
         </is>
       </c>
       <c r="D26" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="84" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>bom_detail</t>
+          <t>warehouse_stock</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Product Costing</t>
+          <t>Gudang Produksi 2</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Staf Gudang (master data, first pass)</t>
         </is>
       </c>
       <c r="D27" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>flow_process_header</t>
+          <t>master_kurs</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -2479,17 +3016,17 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D28" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="28" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>flow_process_detail</t>
+          <t>history_purchase</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -2499,7 +3036,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Purchasing</t>
         </is>
       </c>
       <c r="D29" s="3" t="b">
@@ -2509,7 +3046,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>man_power_rate</t>
+          <t>price_reference_header</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -2519,7 +3056,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D30" s="3" t="b">
@@ -2529,7 +3066,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>rate_bahan_pendukung_foh</t>
+          <t>price_reference_detail</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -2539,17 +3076,17 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D31" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="28" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>rate_generals</t>
+          <t>bom_header</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2559,17 +3096,17 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="D32" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="28" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>product_costing_header</t>
+          <t>bom_detail</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -2579,37 +3116,37 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="D33" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="84" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>product_costing_detail</t>
+          <t>master_standard_material</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Product Costing</t>
+          <t>Master Material</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Engineering (master data, first pass)</t>
         </is>
       </c>
       <c r="D34" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="28" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>material_cost</t>
+          <t>flow_process_header</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2619,17 +3156,17 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="D35" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="28" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>man_power_cost</t>
+          <t>flow_process_detail</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -2639,7 +3176,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="D36" s="3" t="b">
@@ -2647,26 +3184,1590 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>man_power_rate</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Costing</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>man_power_rate_component</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Product Costing</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Costing</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>rate_borongan_helper</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Costing</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>rate_bahan_pendukung_foh</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Costing</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>rate_generals</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Costing</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>product_costing_header</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>Accounting</t>
         </is>
       </c>
-      <c r="D37" t="b">
+      <c r="D42" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>material_cost</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>man_power_cost</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>faktor_indirect_labor</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Costing</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K89"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Kode</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Halaman</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Jenis</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Tujuan</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Use Case</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Akses</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Catatan</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Asal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>PG-01</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Produksi</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Laporan Unpacking Coil</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>/unpack_coil · /unpack_coil/add · /unpack_coil/edit/{id} · /unpack_coil/view/{id}</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Halaman CI3 ×4 (modul/controller)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Operator mencatat Laporan Unpacking Coil dari stok Gudang Produksi 2: pilih pack, material, dan baby coil; simpan, ubah, kunci.</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>UC-01</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Operator: K</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Modul sudah ada (index, add, edit, view, save, update, lock); kesesuaian dengan FR-04 belum diverifikasi. Sudah ada di program saat ini; mockup tidak dibuat (user 2026-10-20).</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>application/modules/unpack_coil</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>PG-02</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Produksi</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Laporan Ketidaksesuaian Material</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>/laporan_ketidaksesuaian</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Halaman CI3 (modul/controller)</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Mencatat ketidaksesuaian material setelah unpacking dan mengirimnya ke proses Claim Material.</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>UC-02</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Admin Produksi: K · PPIC: L</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Sudah ada di program saat ini; mockup tidak dibuat (user 2026-10-20). Path perlu dikonfirmasi dari program (sebelumnya usulan).</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>program saat ini (sudah ada; modul CI3 belum dipetakan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>PG-03</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Produksi</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Release Material Coil</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>/laporan_ketidaksesuaian/release</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Halaman CI3 (modul/controller)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>PPIC melepas kembali Material Coil untuk produksi setelah proses Claim Material selesai.</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>UC-03</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>PPIC: S</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Sudah ada di program saat ini; mockup tidak dibuat (user 2026-10-20). Path perlu dikonfirmasi dari program (sebelumnya usulan); antrean keputusan aktor lain, jadi halaman terpisah dari PG-02.</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>program saat ini (sudah ada; modul CI3 belum dipetakan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>PG-04</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Produksi</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Laporan Produksi</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>/production_report · /production_report/create/{spk} · /production_report/view/{id}</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Halaman CI3 ×3 (modul/controller)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Daftar SPK menunggu produksi, lalu membuat/melihat Laporan Produksi: Add Coil (Unpack/WIP/Hold), FG KW1 dan KW2, Stok Bebas, Sisa Coil, Hold Coil, reject dan scrap, verifikasi selisih berat, submit.</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>UC-04, UC-05, UC-06, UC-07, UC-08, UC-09, UC-10, UC-N01, UC-N02, UC-N03, UC-N04</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Admin Produksi: K</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>menu Produksi (Daftar SPK, Input Produksi). Satu aktor, satu sitting, satu entitas (production_reports); 11 UC dalam satu halaman bersektor. Modul sudah ada (index, ajax_spk_list, create, ajax_get_coils, save, view).</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>application/modules/production_report; ui-mockup/beranda.html, ui-mockup/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>PG-05</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Produksi</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Laporan HPP dan Posting Jurnal</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>/production_report/hpp/{id} · /gl_interface</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Halaman CI3 ×2 (modul/controller)</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Accounting melihat Laporan HPP dan memposting Jurnal Produksi ke GL Interface (satu per satu atau batch).</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>UC-11</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Accounting: K</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>menu Produksi (HPP). Modul gl_interface sudah ada (index, data, detail, view, post, post_batch).</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>application/modules/gl_interface; application/modules/production_report (view_hpp); ui-mockup/hpp.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>PG-06</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Master Produk</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>/product_master (+ /product_type, /product_category, /product_jenis untuk Level 1–3)</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Halaman CI3 ×4 (modul/controller)</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Engineering mengelola produk 4 level beserta Lebar, Tebal, dan Panjang.</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>UC-N05</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Engineering: K</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>menu Master Data. Tumpang tindih: modul sudah ada (tabel product_lvl_4 dan product_lvl_2); mockup menyatukan empat level dalam satu halaman. Terjawab dari kode: Tebal (tebal) dan Panjang (panjang) sudah ada; Lebar memakai kolom wide yang sudah ada (mm, juga dipakai CBM) — tidak ada kolom lebar baru (D1, 2026-10-20).</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>application/modules/product_master (+ product_type, product_category, product_jenis); ui-mockup/pc-produk.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>PG-07</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Master Material</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>/material_master (+ /material_type, /material_category, /material_jenis untuk Level 1–3)</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Halaman CI3 ×4 (modul/controller)</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Engineering mengelola material (Metal Type, Slit, Boron, Material Name, Width, Thickness).</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>UC-N06</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Engineering: K</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>menu Master Data. Tumpang tindih: modul sudah ada (tabel new_inventory_4, ms_coating, ms_tensile). Rev.1: Berat/Meter dihapus dari master (FR-38).</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>application/modules/material_master (+ material_type, material_category, material_jenis); ui-mockup/pc-material.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>PG-08</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Master Standard Material</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>/master_standard_material</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Halaman CI3 (form tunggal)</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Engineering menetapkan Standar Toleransi, Standar Berat Jenis, dan Coating (global).</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>UC-N15</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Engineering: K</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>usulan: satu set nilai global, tanpa label satuan. Modul master_coating (tabel ms_coating) menyimpan jenis coating — tumpang tindih konsep Coating; putuskan saat plan.</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>ui-mockup/pc-standard.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>PG-09</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>BOM Produk</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>/bom · /bom/add · /bom/edit/{id} · /bom/view/{id}</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Halaman CI3 ×4 (modul/controller)</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Engineering menyusun BOM per Varian Tebal; Berat/Meter dihitung otomatis dari Master Standard.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>UC-N09</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Engineering: K</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>menu Master Data. Tumpang tindih: modul sudah ada (tabel ms_bom_header, ms_bom_detail). Rev.1 menambah Berat/Meter terhitung, Varian Tebal, dan aturan unik produk + material.</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>application/modules/bom; ui-mockup/pc-bom.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>PG-10</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Flow Process dan Cycletime</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>/flow_process</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Halaman CI3 (modul/controller)</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Engineering menyusun alur proses per Product Category beserta cycletime; Total Man Hour dihitung otomatis.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>UC-N10</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Engineering: K</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>usulan: belum ada modul yang serupa (master_rate_labor/process_product adalah rate per proses, konsep berbeda).</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>ui-mockup/pc-flow.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>PG-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Kurs</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>/master_kurs</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Halaman CI3 (modul/controller)</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Finance mengelola kurs mata uang terhadap Rupiah.</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>UC-N07</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Finance: K</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>usulan. Tumpang tindih sebagian: modul mata_uang (daftar mata uang, tabel mata_uang) sudah ada; periksa apakah kolom kurs ada.</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>ui-mockup/pc-kurs.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>PG-12</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Master Data</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Price Reference</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>/price_ref_raw_material</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Halaman CI3 (modul/controller)</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Finance memperbarui Price Reference USD/Kg per material (acuan Max History Pembelian); sistem menghitung Rp/Kg.</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>UC-N08</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Finance: K</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>menu Master Data. Tumpang tindih: modul sudah ada (tabel new_inventory_4 dengan kolom price_ref, price_ref_high, price_ref_usd; kesamaan dengan Max belum diverifikasi). price_sup_raw_material menyimpan harga supplier.</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>application/modules/price_ref_raw_material (+ price_sup_raw_material); ui-mockup/pc-price-reference.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>PG-13</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Man Power Rate (Operator)</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>/master_rate_labor</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Halaman CI3 (modul/controller)</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Costing mengisi komponen gaji/BPJS/lain-lain Operator, jam kerja, dan porsi Operator; sistem menghitung Rate 1/3 Operator.</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>UC-N11</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Costing: K</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>menu Rate. Tumpang tindih: modul master_rate_labor sudah ada (tabel ms_rate_labor jenis direct/indirect, ms_rate_process_product); struktur berbeda dari Rev.1, periksa saat plan.</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>application/modules/master_rate_labor; ui-mockup/pc-man-power-rate.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>PG-14</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Rate Bahan Pendukung dan FOH</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>/rate_bahan_pendukung_foh</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Halaman CI3 (modul/controller)</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Costing menetapkan Rate Bahan Pendukung Khusus dan Rate FOH (Rp/Kg) per Product Category.</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>UC-N12</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Costing: K</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>usulan.</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>ui-mockup/pc-bpk-foh.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>PG-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>General Rate</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>/rate_generals</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Halaman CI3 (form tunggal)</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Costing menetapkan Rate Consumables, Scrap, Biaya Koordinasi, dan enam Rate Other Cost (berlaku semua produk).</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>UC-N13</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Costing: K</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>usulan.</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>ui-mockup/pc-general-rate.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>PG-16</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Negotiation Allowance</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>/rate_negotiation_allowance</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Halaman CI3 (modul/controller)</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Sales menetapkan Rate Negotiation Allowance (%) per Product Category.</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>UC-12</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Sales: K</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>usulan: aktor Sales, jadi halaman terpisah dari General Rate (Costing).</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>ui-mockup/pc-negotiation.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>PG-17</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Hasil dan Pricelist</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Simulasi Costing</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>/product_costing</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Halaman CI3 (daftar + modal Report Costing Detail)</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Melihat hasil costing per Produk × varian BOM dari Material Cost sampai Bottom Price (Rp/Meter dan Rp/Kg), dengan Report Costing Detail/Produk.</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>UC-N14</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Accounting: L · Sales: L · Engineering: L</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>usulan. Halaman baca; perhitungan otomatis. Report Costing Detail ditampilkan di sini pada mockup padahal dihasilkan oleh sub-flow UC-13 (lihat usulan di laporan).</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>ui-mockup/pc-simulasi.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>PG-18</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Hasil dan Pricelist</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Pricelist</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>/pricelist</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Halaman CI3 (modul/controller)</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Sales menghitung Price List per Produk × varian BOM, menyusun Draft Pricelist, dan mengajukannya ke Management.</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>UC-13</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Sales: K</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>usulan.</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>ui-mockup/pc-pricelist.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>PG-19</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Hasil dan Pricelist</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Approval Pricelist</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>/pricelist/approval</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Halaman CI3 (antrean keputusan)</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Management menyetujui atau menolak Draft Pricelist; Reject wajib beralasan.</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>UC-14</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Management: S · Sales: L (alasan Reject)</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>usulan: antrean keputusan aktor lain, halaman terpisah.</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>ui-mockup/pc-approval.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>PG-20</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Hasil dan Pricelist</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Product Catalog</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>/product_catalog</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Halaman CI3 (modul/controller)</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Sales merilis Product Catalog dari pricelist yang sudah Approved (snapshot harga).</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>UC-15</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Sales: K</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>usulan.</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>ui-mockup/pc-catalog.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="56" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>PG-21</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Rate Borongan Helper</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>/rate_borongan_helper</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Halaman CI3 (modul/controller)</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Costing menetapkan Rate Borongan Helper per Product Category dalam Rp/Meter (satu-satunya satuan).</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>UC-N16</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Costing: K</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>menu Rate, terpisah dari Man Power Rate (user 2026-10-20). Path usulan; modul master_rate_labor (ms_rate_labor jenis direct/indirect, ms_rate_process_product) tumpang tindih sebagian, periksa saat plan.</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>baru; ui-mockup/pc-borongan.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="56" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>PG-22</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Faktor Indirect Labor</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>/faktor_indirect_labor</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Halaman CI3 (modul/controller)</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Costing menetapkan Faktor Indirect Labor (satu nilai global) yang mengalikan jumlah bagian Operator dan Borongan pada Man Power Cost.</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>UC-N17</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Costing: K</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>menu Rate, terpisah dari Man Power Rate (user 2026-10-20). Path usulan; modul master_rate_labor (ms_rate_labor jenis direct/indirect) mungkin tumpang tindih, periksa saat plan.</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>baru; ui-mockup/pc-faktor-indirect.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/specs/docs/workbook.xlsx
+++ b/specs/docs/workbook.xlsx
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Tetapkan Rate Negotiation Allowance (Extra Margin) per Product Category</t>
+          <t>Ajukan Perubahan Rate Negotiation Allowance (Extra Margin) per Product Category</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Sales Manager</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Product Category; Rate Negotiation Allowance (Extra Margin, %)</t>
+          <t>Product Category; Rate Negotiation Allowance (Extra Margin, %) yang diajukan</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>FR-55 (user 2026-10-19). 1) Sales membuka daftar Rate Negotiation Allowance. 2) Sales menambah/mengubah/menghapus rate (%) per Product Category. 3) Sistem menyimpan, mengisi Latest Update dan Updated By, lalu menampilkan kembali daftar. Rate dipakai UC-13: Price List = Bottom Price + (Rate × Bottom Price); bukan lagi bagian Rate Generals. Dikerjakan berkala sesuai kebijakan. (Rev.1 UC-10; BPMN D05: 'Penetapan Rate Negotiation Allowance (Extra Margin)', lane Sales.)</t>
+          <t>FR-55 (direvisi 2026-10-21), FR-67. Prasyarat: produk sudah ada di Product Catalog (BPMN To Be Sales D01). 1) Sales Manager menilai "Perlu perubahan margin?" (acuan penilaian customer baru: toko sewa/sendiri, lama berdiri, armada, asset, jumlah cabang; tidak diotomasi). 2) Bila perlu, Sales Manager membuka halaman Negotiation Allowance dan mengajukan rate Extra Margin (%) baru untuk satu Product Category (angka ≥ 0, titik sebagai desimal; diasumsikan satu pengajuan per kategori, OQ 22). 3) Sistem menyimpan pengajuan berstatus Menunggu Approval GM beserta pengaju dan waktu; rate aktif TIDAK berubah, sehingga Simulasi, Pricelist, dan Katalog tetap memakai rate aktif. 4) Bila GM menolak (UC-16), pengajuan berstatus Rejected dengan alasan; Sales Manager memperbaiki lalu mengajukan ulang (pengajuan baru). Rate aktif dipakai UC-13: Price List = Bottom Price + (Rate × Bottom Price). Persetujuan diskon pada Quotation (&lt;5% Sales langsung, 5–10% Sales Manager, &gt;10% GM) di luar scope Product Costing. (Rev.1 UC-10, direvisi oleh BPMN To Be Sales D01 dan keputusan user 2026-10-21: perubahan rate perlu approval GM; BPMN D05: "Penetapan Rate Negotiation Allowance (Extra Margin)".)</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Rate Negotiation Allowance per Product Category tersimpan, siap dipakai untuk generate Pricelist</t>
+          <t>Pengajuan perubahan rate berstatus Menunggu Approval GM tersimpan; rate aktif tidak berubah sampai disetujui GM (UC-16)</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>rate_negotiation_allowance</t>
+          <t>rate_negotiation_allowance_request, rate_negotiation_allowance</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>FR-47, FR-57, FR-58. Prasyarat: hasil costing sampai Bottom Price (UC-N14) dan UC-12 tersedia. 1) Sales memilih Produk (dan varian BOM) dan menerima Bottom Price dari hasil costing. 2) Sistem menghitung Price List = Bottom Price + (Rate Negotiation Allowance kategori × Bottom Price), Rp/Meter dan Rp/Kg, serta Pricelist Produk/Meter (= Ukuran Produk × Price List/Meter) dan Pricelist Produk/Kg sebagai pembanding terhadap Pricelist HFG saat ini (contoh 27.400 Rp/Meter, hanya contoh). 3) Sistem menghasilkan Report Costing Detail/Produk. 4) Sales menyusun Draft Pricelist per Produk × varian BOM (status Draft) dan mengirimnya ke Management (Menunggu Approval). Bila Management menolak (UC-14), Sales menghitung ulang dengan alasan Reject terlihat lalu mengajukan lagi. (Rev.1 UC-16 dan UC-17; BPMN D05: User task 'Pengajuan Approval Pricelist', service task 'Perhitungan Price List' dan dokumen 'Report Costing Detail/Product' dilipat.) Revisi 2026-10-20 (FR-59): Draft Pricelist boleh disimpan, tetapi tidak boleh diajukan ke Management selama ada baris yang datanya belum lengkap (rate, Price Reference, Faktor Indirect Labor, dst.); sistem menyebut kekurangan dan menu untuk mengisinya.</t>
+          <t>FR-47, FR-57, FR-58. Prasyarat: hasil costing sampai Bottom Price (UC-N14) dan rate Negotiation Allowance aktif tersedia (rate berubah hanya setelah pengajuan UC-12 disetujui GM di UC-16). 1) Sales memilih Produk (dan varian BOM) dan menerima Bottom Price dari hasil costing. 2) Sistem menghitung Price List = Bottom Price + (Rate Negotiation Allowance kategori × Bottom Price), Rp/Meter dan Rp/Kg, serta Pricelist Produk/Meter (= Ukuran Produk × Price List/Meter) dan Pricelist Produk/Kg sebagai pembanding terhadap Pricelist HFG saat ini (contoh 27.400 Rp/Meter, hanya contoh). 3) Sistem menghasilkan Report Costing Detail/Produk. 4) Sales menyusun Draft Pricelist per Produk × varian BOM (status Draft) dan mengirimnya ke Management (Menunggu Approval). Bila Management menolak (UC-14), Sales menghitung ulang dengan alasan Reject terlihat lalu mengajukan lagi. (Rev.1 UC-16 dan UC-17; BPMN D05: User task 'Pengajuan Approval Pricelist', service task 'Perhitungan Price List' dan dokumen 'Report Costing Detail/Product' dilipat.) Revisi 2026-10-20 (FR-59): Draft Pricelist boleh disimpan, tetapi tidak boleh diajukan ke Management selama ada baris yang datanya belum lengkap (rate, Price Reference, Faktor Indirect Labor, dst.); sistem menyebut kekurangan dan menu untuk mengisinya.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1443,7 +1443,53 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
+    <row r="17" ht="224" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>UC-16</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Setujui / Tolak Perubahan Rate Extra Margin</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Pengajuan perubahan rate Negotiation Allowance yang Menunggu Approval GM; keputusan Approve atau Reject; alasan Reject (wajib; diasumsikan, OQ 20)</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>FR-67. Prasyarat: pengajuan berstatus Menunggu Approval GM (UC-12). 1) GM membuka antrean pengajuan perubahan rate Extra Margin. 2) GM membandingkan rate aktif dengan rate yang diajukan per Product Category, lalu memutuskan Approve atau Reject (alasan Reject wajib; diasumsikan, mohon konfirmasi). 3) Approve: sistem memperbarui rate aktif (rate_negotiation_allowance, latest_update, updated_by) dan menyimpan status Approved, decided_by, decided_at; rate baru dipakai Simulasi, Pricelist baru, dan Katalog berikutnya, sedangkan Pricelist yang sudah diajukan tidak berubah (snapshot, FR-58). 4) Reject: sistem menyimpan status Rejected, decided_by, decided_at, reject_reason; rate aktif tidak berubah; Sales Manager memperbaiki lalu mengajukan ulang (UC-12). Status pengajuan hanya Menunggu Approval GM, Approved, Rejected. (BPMN To Be Sales D01: gateway "Approval Extra Margin" di lane GM, Approved → Buat Quotation, Reject → "Update dan Ajukan Rate Extra Margin baru"; dijadikan UC karena keputusannya dibuat manusia.)</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Pengajuan Approved (rate aktif diperbarui) atau Rejected dengan alasan (kembali ke Sales Manager, UC-12)</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>rate_negotiation_allowance_request, rate_negotiation_allowance</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>PG-23</t>
+        </is>
+      </c>
+    </row>
     <row r="18"/>
     <row r="19"/>
     <row r="20"/>
@@ -1517,7 +1563,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="10" customWidth="1" style="1" min="1" max="1"/>
@@ -2380,34 +2426,948 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D129"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <cols>
+    <col width="28" customWidth="1" style="1" min="1" max="1"/>
+    <col width="16" customWidth="1" style="1" min="2" max="2"/>
+    <col width="8" customWidth="1" style="4" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Entity yang dibutuhkan</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Modul</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>ERD</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>tr_unpack_coil_header</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Unpack</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>warehouse_pack</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Unpack</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>baby_coil</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Unpack</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="84" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Master Material</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Engineering (master data, first pass)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="84" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>gudang_produksi_2</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Gudang Produksi 2</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Staf Gudang (master data, first pass)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>laporan_ketidaksesuaian_material</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Report Produksi</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>material_coil</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Report Produksi</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>PPIC</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>production_report_items</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Report Produksi</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Admin Produksi</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="84" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>product_lvl_4</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Master Product</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Engineering (master data, first pass)</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>production_report_scraps</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Report Produksi</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Admin Produksi</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>production_reports</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Report Produksi</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Admin Produksi</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>stok_gudang_wip</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Report Produksi</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Admin Produksi</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="98" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>production_plan</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Production Plan (Eksternal)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Production Planning (eksternal, read-only)</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="98" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>asset</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Master Asset</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Staf Produksi (master data, first pass)</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="98" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Master Employee</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Admin Produksi (master data, first pass)</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>jurnal_produksi</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Report HPP</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>gl_interface</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Report HPP</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>rate_negotiation_allowance</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>pricelist_header</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>pricelist_detail</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>product_costing_detail</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>product_catalog_header</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>product_catalog_detail</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" ht="84" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>gudang_material_hold</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Gudang Produksi 2</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Staf Gudang (master data, first pass)</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>production_report_materials</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Report Produksi</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Admin Produksi</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" ht="84" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>warehouse_stock</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Gudang Produksi 2</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Staf Gudang (master data, first pass)</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>master_kurs</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>history_purchase</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Purchasing</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>price_reference_header</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>price_reference_detail</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>bom_header</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>bom_detail</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" ht="84" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>master_standard_material</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Master Material</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Engineering (master data, first pass)</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>flow_process_header</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>flow_process_detail</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>man_power_rate</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Costing</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>man_power_rate_component</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Costing</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>rate_borongan_helper</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Costing</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>rate_bahan_pendukung_foh</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Costing</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>rate_generals</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Costing</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>product_costing_header</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>material_cost</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>man_power_cost</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>faktor_indirect_labor</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Costing</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>rate_negotiation_allowance_request</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
     <row r="47"/>
     <row r="48"/>
     <row r="49"/>
@@ -2441,928 +3401,56 @@
     <row r="77"/>
     <row r="78"/>
     <row r="79"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D45"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
-  <cols>
-    <col width="28" customWidth="1" style="1" min="1" max="1"/>
-    <col width="16" customWidth="1" style="1" min="2" max="2"/>
-    <col width="8" customWidth="1" style="4" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Entity yang dibutuhkan</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Modul</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>ERD</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>tr_unpack_coil_header</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Unpack</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Operator</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>warehouse_pack</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Unpack</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Operator</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>baby_coil</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Unpack</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Operator</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" ht="84" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Master Material</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Engineering (master data, first pass)</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" ht="84" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>gudang_produksi_2</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Gudang Produksi 2</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Staf Gudang (master data, first pass)</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>laporan_ketidaksesuaian_material</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Report Produksi</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Operator</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>material_coil</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Report Produksi</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>PPIC</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>production_report_items</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Report Produksi</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Admin Produksi</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" ht="84" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>product_lvl_4</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Master Product</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Engineering (master data, first pass)</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>production_report_scraps</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Report Produksi</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Admin Produksi</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>production_reports</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Report Produksi</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Admin Produksi</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>stok_gudang_wip</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Report Produksi</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Admin Produksi</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" ht="98" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>production_plan</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Production Plan (Eksternal)</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Production Planning (eksternal, read-only)</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" ht="98" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>asset</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Master Asset</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Staf Produksi (master data, first pass)</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" ht="98" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>employee</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Master Employee</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Admin Produksi (master data, first pass)</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>jurnal_produksi</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Report HPP</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Accounting</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>gl_interface</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Report HPP</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Accounting</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>rate_negotiation_allowance</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Product Costing</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>pricelist_header</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Product Costing</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>pricelist_detail</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Product Costing</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>product_costing_detail</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Product Costing</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Accounting</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>product_catalog_header</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Product Costing</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>product_catalog_detail</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Product Costing</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" ht="84" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>gudang_material_hold</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Gudang Produksi 2</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Staf Gudang (master data, first pass)</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" ht="42" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>production_report_materials</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Report Produksi</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Admin Produksi</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" ht="84" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>warehouse_stock</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Gudang Produksi 2</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Staf Gudang (master data, first pass)</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>master_kurs</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Product Costing</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>history_purchase</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Product Costing</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Purchasing</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>price_reference_header</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Product Costing</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>price_reference_detail</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Product Costing</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>bom_header</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Product Costing</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>bom_detail</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Product Costing</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" ht="84" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>master_standard_material</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Master Material</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>Engineering (master data, first pass)</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>flow_process_header</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Product Costing</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>flow_process_detail</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Product Costing</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>man_power_rate</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Product Costing</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>Costing</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>man_power_rate_component</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Product Costing</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>Costing</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>rate_borongan_helper</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>Product Costing</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>Costing</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>rate_bahan_pendukung_foh</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Product Costing</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>Costing</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>rate_generals</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Product Costing</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>Costing</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>product_costing_header</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Product Costing</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>Accounting</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>material_cost</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Product Costing</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>Accounting</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>man_power_cost</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Product Costing</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>Accounting</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>faktor_indirect_labor</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Product Costing</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>Costing</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4330,7 +4418,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Sales menetapkan Rate Negotiation Allowance (%) per Product Category.</t>
+          <t>Sales Manager mengajukan perubahan Rate Negotiation Allowance (Extra Margin, %) per Product Category; rate aktif tidak berubah sampai disetujui GM (UC-16).</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -4340,7 +4428,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Sales: K</t>
+          <t>Sales Manager: K · GM: L</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -4350,7 +4438,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>usulan: aktor Sales, jadi halaman terpisah dari General Rate (Costing).</t>
+          <t>usulan: aktor Sales Manager (BPMN Sales D01), jadi halaman terpisah dari General Rate (Costing). Menampilkan rate aktif dan status pengajuan.</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -4701,7 +4789,63 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>PG-23</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Approval Extra Margin</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>/rate_negotiation_allowance/approval</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Halaman CI3 (antrean keputusan)</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>GM menyetujui atau menolak pengajuan perubahan Rate Negotiation Allowance (Extra Margin); Reject wajib beralasan (diasumsikan).</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>UC-16</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>GM: S · Sales Manager: L (alasan Reject)</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>usulan: antrean keputusan aktor lain (GM), halaman terpisah dari PG-16 dan dari Approval Pricelist (PG-19, Management); Area Rate karena objeknya rate master, bukan pricelist.</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>ui-mockup/pc-approval-extra-margin.html</t>
+        </is>
+      </c>
+    </row>
     <row r="25"/>
     <row r="26"/>
     <row r="27"/>

--- a/specs/docs/workbook.xlsx
+++ b/specs/docs/workbook.xlsx
@@ -660,7 +660,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1490,68 +1490,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1563,7 +1501,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="10" customWidth="1" style="1" min="1" max="1"/>
@@ -2426,6 +2364,53 @@
         </is>
       </c>
     </row>
+    <row r="19" ht="409.5" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>UC-N18</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Tinjau Perubahan Bottom Price</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Notifikasi perubahan Bottom Price (per Produk × varian BOM, dikelompokkan per Product Category); keputusan "Ajukan Rate Extra Margin Baru" atau "Tidak Perlu Diubah"; catatan (opsional)</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>FR-68, FR-69, FR-70, NFR-16 (diusulkan; ambang, pembanding harga, peninjau, dan kanal sudah dikonfirmasi user 2026-10-21 — OQ 25, 27, 28; sisanya diasumsikan, mohon konfirmasi OQ 26, 29–33). 1) Sistem membandingkan Bottom Price (Rp/Meter dan Rp/Kg) tiap Produk × varian BOM dengan baseline setiap kali costing dihitung; bila berbeda (naik atau turun, apa pun penyebabnya) sistem membuat notifikasi berstatus Belum Ditinjau (langkah otomatis, tanpa aktor). 2) Sales (Staf Sales atau Sales Manager) membuka dashboard notifikasi; notifikasi dikelompokkan per Product Category dan jumlah yang belum ditinjau tampil sebagai lencana di menu. 3) Sales membandingkan Bottom Price lama dan baru, selisih (Rp dan %), komponen yang berubah, Rate Extra Margin aktif, harga jual saat ini terhadap Price List baru bila rate lama dipertahankan. 4) Sales memilih: a) Ajukan Rate Extra Margin Baru: membuka pengajuan UC-12 untuk Product Category itu, lalu GM memutuskan di UC-16 (FR-67); status Diajukan Extra Margin Baru dan terhubung ke pengajuan; b) Tidak Perlu Diubah (catatan opsional): status Tidak Perlu Diubah. 5) Kedua keputusan mencatat peninjau, waktu, dan catatan, ditulis ke log, dan menggeser baseline ke Bottom Price baru. Sistem tidak mengubah rate, Pricelist, atau Katalog secara otomatis. Semua Sales dapat meninjau; kanal hanya dashboard (tanpa email/WhatsApp) dan tanpa batas waktu tinjau; ambang: perubahan sekecil apa pun (≥ Rp0,01). Di luar scope: persetujuan diskon Quotation. (Permintaan user 2026-10-21; terkait BPMN To Be Sales D01, gateway "Perlu Perubahan Margin?".)</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Notifikasi tertinjau: status Diajukan Extra Margin Baru (terhubung ke pengajuan UC-12) atau Tidak Perlu Diubah, dengan peninjau, waktu, dan catatan</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>bottom_price_notification, rate_negotiation_allowance, rate_negotiation_allowance_request, product_costing_detail</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>PG-24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2437,7 +2422,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D129"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="28" customWidth="1" style="1" min="1" max="1"/>
@@ -3368,89 +3353,26 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>bottom_price_notification</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3462,7 +3384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K89"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4846,71 +4768,63 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>PG-24</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Hasil dan Pricelist</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Dashboard Notifikasi Bottom Price</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>/bottom_price_notification</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Halaman CI3 (daftar + modal Report Costing Detail)</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Menampilkan notifikasi bila Bottom Price Produk × varian BOM berubah (Bottom Price lama → baru, selisih, Rate Extra Margin aktif, harga jual saat ini vs Price List baru) agar Sales memutuskan Ajukan Rate Extra Margin Baru atau Tidak Perlu Diubah.</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>UC-N18</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Sales: K (Staf Sales dan Sales Manager)</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>menu Hasil &amp; Pricelist; lencana jumlah notifikasi Belum Ditinjau di menu. Fitur diusulkan (FR-68–FR-70, NFR-16); rincian diasumsikan, open question 26, 29–33 (25, 27, 28 terjawab 2026-10-21). Path usulan.</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>baru (usulan); ui-mockup/pc-notifikasi-bottom-price.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/specs/docs/workbook.xlsx
+++ b/specs/docs/workbook.xlsx
@@ -2392,7 +2392,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>FR-68, FR-69, FR-70, NFR-16 (diusulkan; ambang, pembanding harga, peninjau, dan kanal sudah dikonfirmasi user 2026-10-21 — OQ 25, 27, 28; sisanya diasumsikan, mohon konfirmasi OQ 26, 29–33). 1) Sistem membandingkan Bottom Price (Rp/Meter dan Rp/Kg) tiap Produk × varian BOM dengan baseline setiap kali costing dihitung; bila berbeda (naik atau turun, apa pun penyebabnya) sistem membuat notifikasi berstatus Belum Ditinjau (langkah otomatis, tanpa aktor). 2) Sales (Staf Sales atau Sales Manager) membuka dashboard notifikasi; notifikasi dikelompokkan per Product Category dan jumlah yang belum ditinjau tampil sebagai lencana di menu. 3) Sales membandingkan Bottom Price lama dan baru, selisih (Rp dan %), komponen yang berubah, Rate Extra Margin aktif, harga jual saat ini terhadap Price List baru bila rate lama dipertahankan. 4) Sales memilih: a) Ajukan Rate Extra Margin Baru: membuka pengajuan UC-12 untuk Product Category itu, lalu GM memutuskan di UC-16 (FR-67); status Diajukan Extra Margin Baru dan terhubung ke pengajuan; b) Tidak Perlu Diubah (catatan opsional): status Tidak Perlu Diubah. 5) Kedua keputusan mencatat peninjau, waktu, dan catatan, ditulis ke log, dan menggeser baseline ke Bottom Price baru. Sistem tidak mengubah rate, Pricelist, atau Katalog secara otomatis. Semua Sales dapat meninjau; kanal hanya dashboard (tanpa email/WhatsApp) dan tanpa batas waktu tinjau; ambang: perubahan sekecil apa pun (≥ Rp0,01). Di luar scope: persetujuan diskon Quotation. (Permintaan user 2026-10-21; terkait BPMN To Be Sales D01, gateway "Perlu Perubahan Margin?".)</t>
+          <t>FR-68, FR-69, FR-70, NFR-16 (diusulkan; seluruh rincian dikonfirmasi user 2026-10-21 — OQ 25–33). 1) Sistem membandingkan Bottom Price (Rp/Meter dan Rp/Kg) tiap Produk × varian BOM dengan baseline setiap kali costing dihitung; bila berbeda (naik atau turun, apa pun penyebabnya) sistem membuat notifikasi berstatus Belum Ditinjau (langkah otomatis, tanpa aktor). 2) Sales (Staf Sales atau Sales Manager) membuka dashboard notifikasi; notifikasi dikelompokkan per Product Category dan jumlah yang belum ditinjau tampil sebagai lencana di menu. 3) Sales membandingkan Bottom Price lama dan baru, selisih (Rp dan %), komponen yang berubah, Rate Extra Margin aktif, harga jual saat ini terhadap Price List baru bila rate lama dipertahankan. 4) Sales memilih: a) Ajukan Rate Extra Margin Baru (hanya Sales Manager; hak akses diatur per pengguna di program): membuka pengajuan UC-12 untuk Product Category itu, lalu GM memutuskan di UC-16 (FR-67); status Diajukan Extra Margin Baru dan terhubung ke pengajuan; b) Tidak Perlu Diubah (catatan opsional): status Tidak Perlu Diubah. 5) Kedua keputusan mencatat peninjau, waktu, dan catatan, ditulis ke log, dan menggeser baseline ke Bottom Price baru. Sistem tidak mengubah rate, Pricelist, atau Katalog secara otomatis. Semua Sales dapat meninjau; kanal hanya dashboard (tanpa email/WhatsApp) dan tanpa batas waktu tinjau; ambang: perubahan sekecil apa pun (≥ Rp0,01). Di luar scope: persetujuan diskon Quotation. (Permintaan user 2026-10-21; terkait BPMN To Be Sales D01, gateway "Perlu Perubahan Margin?".)</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Sales: K (Staf Sales dan Sales Manager)</t>
+          <t>Sales: K (lihat dan Tidak Perlu Diubah; Staf Sales dan Sales Manager) · Sales Manager: K (Ajukan Rate Extra Margin Baru; hak akses per pengguna di program)</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>menu Hasil &amp; Pricelist; lencana jumlah notifikasi Belum Ditinjau di menu. Fitur diusulkan (FR-68–FR-70, NFR-16); rincian diasumsikan, open question 26, 29–33 (25, 27, 28 terjawab 2026-10-21). Path usulan.</t>
+          <t>menu Hasil &amp; Pricelist; lencana jumlah notifikasi Belum Ditinjau di menu. Fitur diusulkan (FR-68–FR-70, NFR-16); rincian diasumsikan, open question 25–33 terjawab 2026-10-21. Path usulan.</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">

--- a/specs/docs/workbook.xlsx
+++ b/specs/docs/workbook.xlsx
@@ -1330,7 +1330,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>FR-47, FR-57, FR-58. Prasyarat: hasil costing sampai Bottom Price (UC-N14) dan rate Negotiation Allowance aktif tersedia (rate berubah hanya setelah pengajuan UC-12 disetujui GM di UC-16). 1) Sales memilih Produk (dan varian BOM) dan menerima Bottom Price dari hasil costing. 2) Sistem menghitung Price List = Bottom Price + (Rate Negotiation Allowance kategori × Bottom Price), Rp/Meter dan Rp/Kg, serta Pricelist Produk/Meter (= Ukuran Produk × Price List/Meter) dan Pricelist Produk/Kg sebagai pembanding terhadap Pricelist HFG saat ini (contoh 27.400 Rp/Meter, hanya contoh). 3) Sistem menghasilkan Report Costing Detail/Produk. 4) Sales menyusun Draft Pricelist per Produk × varian BOM (status Draft) dan mengirimnya ke Management (Menunggu Approval). Bila Management menolak (UC-14), Sales menghitung ulang dengan alasan Reject terlihat lalu mengajukan lagi. (Rev.1 UC-16 dan UC-17; BPMN D05: User task 'Pengajuan Approval Pricelist', service task 'Perhitungan Price List' dan dokumen 'Report Costing Detail/Product' dilipat.) Revisi 2026-10-20 (FR-59): Draft Pricelist boleh disimpan, tetapi tidak boleh diajukan ke Management selama ada baris yang datanya belum lengkap (rate, Price Reference, Faktor Indirect Labor, dst.); sistem menyebut kekurangan dan menu untuk mengisinya.</t>
+          <t>FR-47, FR-57, FR-58. Prasyarat: hasil costing sampai Bottom Price (UC-N14) dan rate Negotiation Allowance aktif tersedia (rate berubah hanya setelah pengajuan UC-12 disetujui GM di UC-16). 1) Sales memilih Produk (dan varian BOM) dan menerima Bottom Price dari hasil costing. 2) Sistem menghitung Price List = Bottom Price + (Rate Negotiation Allowance kategori × Bottom Price), Rp/Meter dan Rp/Kg, serta Pricelist Produk/Meter (= Ukuran Produk × Price List/Meter) dan Pricelist Produk/Kg sebagai pembanding terhadap Pricelist HFG saat ini (contoh 27.400 Rp/Meter, hanya contoh). 3) Sistem menghasilkan Report Costing Detail/Produk. 4) Sales menyusun Draft Pricelist per Produk × varian BOM (status Draft) dan mengirimnya ke Management (Menunggu Approval). Bila Management menolak (UC-14), Sales menghitung ulang dengan alasan Reject terlihat lalu mengajukan lagi. (Rev.1 UC-16 dan UC-17; BPMN D05: User task 'Pengajuan Approval Pricelist', service task 'Perhitungan Price List' dan dokumen 'Report Costing Detail/Product' dilipat.) Revisi 2026-10-20 (FR-59): Draft Pricelist boleh disimpan, tetapi tidak boleh diajukan ke Management selama ada baris yang datanya belum lengkap (rate, Price Reference, Faktor Indirect Labor, dst.); sistem menyebut kekurangan dan menu untuk mengisinya. Tampilan daftar (revisi 2026-10-21, FR-73): nama produk (dengan varian/Uniq ID) di depan; nomor Pricelist/katalog menjadi kolom sekunder.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>FR-58. Prasyarat: pricelist Approved (UC-14). 1) Sales memilih Pricelist yang sudah Approved dan merilis Product Catalog. 2) Sistem menyimpan snapshot harga yang disetujui per Produk × varian BOM beserta released_by dan released_at (product_catalog_header/detail). 3) Product Catalog diteruskan ke proses Sales (di luar alur ini). Hanya pricelist Approved yang boleh dirilis; satu pricelist Approved boleh dirilis berkali-kali dan setiap rilis membuat Product Catalog (snapshot) baru (user 2026-10-20). (Rev.1 UC-18; BPMN D05 menggambarnya dengan ikon roda gigi, tetapi Use Case Rev.1 menyebut Sales yang merilis.)</t>
+          <t>FR-58. Prasyarat: pricelist Approved (UC-14). 1) Sales memilih Pricelist yang sudah Approved dan merilis Product Catalog. 2) Sistem menyimpan snapshot harga yang disetujui per Produk × varian BOM beserta released_by dan released_at (product_catalog_header/detail). 3) Product Catalog diteruskan ke proses Sales (di luar alur ini). Hanya pricelist Approved yang boleh dirilis; satu pricelist Approved boleh dirilis berkali-kali dan setiap rilis membuat Product Catalog (snapshot) baru (user 2026-10-20). (Rev.1 UC-18; BPMN D05 menggambarnya dengan ikon roda gigi, tetapi Use Case Rev.1 menyebut Sales yang merilis.) Tampilan daftar (revisi 2026-10-21, FR-73): nama produk (dengan varian/Uniq ID) di depan; nomor Pricelist/katalog menjadi kolom sekunder.</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1501,7 +1501,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="10" customWidth="1" style="1" min="1" max="1"/>
@@ -2411,6 +2411,158 @@
         </is>
       </c>
     </row>
+    <row r="20" ht="409.5" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>UC-N19</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Lihat History Costing</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Costing / Accounting / Sales / Management</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Filter: produk, Product Category, periode, sumber perubahan; pilihan catatan riwayat untuk melihat detail snapshot</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>FR-71, NFR-17 (diusulkan; rincian diasumsikan, mohon konfirmasi OQ 34–42). 1) Setiap kali perubahan master, rate, atau input costing membuat Bottom Price suatu Produk × varian BOM berubah, sistem menyimpan satu catatan riwayat per Produk × varian BOM (langkah otomatis, tanpa aktor): waktu, pengguna yang mengubah, sumber perubahan (master/rate yang diubah, nilai lama → baru), Bottom Price lama → baru (Rp/Meter dan Rp/Kg), snapshot komponen costing lama dan baru, dan Rate Extra Margin aktif. 2) Pengguna membuka halaman History Costing. 3) Pengguna menyaring menurut produk, Product Category, periode, dan sumber perubahan. 4) Pengguna membuka detail untuk melihat snapshot komponen lama dan baru. Riwayat hanya baca (tidak dapat diubah atau dihapus), dan terpisah dari Notifikasi Bottom Price (UC-N18): notifikasi untuk Sales meninjau, riwayat untuk audit. (Permintaan user 2026-10-21.)</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Daftar riwayat perubahan Bottom Price dengan detail snapshot komponen lama dan baru</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>history_costing, product_costing_detail</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>PG-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="409.5" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>UC-N20</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Lihat History Price List</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Costing / Accounting / Sales / Management</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Filter: produk, Product Category, periode, kejadian; pilihan catatan riwayat untuk melihat detail</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>FR-72, NFR-17 (diusulkan; rincian diasumsikan, mohon konfirmasi OQ 34–42; terhubung ke FR-58 dan FR-67). 1) Setiap kejadian pada Pricelist disimpan per Produk × varian BOM (langkah otomatis, tanpa aktor): Diajukan, Disetujui (Approved), Ditolak (Rejected, beserta alasan), Dihitung Ulang (kembali ke Draft), atau Dirilis ke Product Catalog; dengan nomor Pricelist, status, waktu, pengguna, Price List lama → baru (Rp/Meter dan Rp/Kg), Bottom Price dan Rate Extra Margin saat itu, serta catatan atau alasan. 2) Pengguna membuka halaman History Price List. 3) Pengguna menyaring menurut produk, Product Category, periode, dan kejadian. 4) Pengguna melihat perubahan Price List lama → baru. Riwayat hanya baca (tidak dapat diubah atau dihapus). (Permintaan user 2026-10-21.)</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Daftar riwayat kejadian Pricelist per Produk × varian BOM dengan Price List lama dan baru</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>history_pricelist, pricelist_header, pricelist_detail, product_catalog_header</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>PG-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2422,7 +2574,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="28" customWidth="1" style="1" min="1" max="1"/>
@@ -3373,6 +3525,196 @@
         <v>1</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>history_costing</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>history_pricelist</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Product Costing</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3384,7 +3726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4474,7 +4816,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>usulan.</t>
+          <t>usulan. Revisi tampilan 2026-10-21 (FR-73): nama produk (dengan varian/Uniq ID) tampil di depan pada daftar; nomor Pricelist/katalog menjadi kolom sekunder.</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
@@ -4588,7 +4930,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>usulan.</t>
+          <t>usulan. Revisi tampilan 2026-10-21 (FR-73): nama produk (dengan varian/Uniq ID) tampil di depan pada daftar; nomor Pricelist/katalog menjadi kolom sekunder.</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -4825,6 +5167,212 @@
         </is>
       </c>
     </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>PG-25</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Hasil dan Pricelist</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>History Costing</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>/history_costing</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Halaman CI3 (daftar + modal detail snapshot)</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Menampilkan riwayat perubahan Bottom Price per Produk × varian BOM (sumber perubahan, nilai lama → baru, snapshot komponen) untuk audit; hanya baca.</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>UC-N19</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Costing, Accounting, Sales, Management: L</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>menu Hasil &amp; Pricelist. Fitur diusulkan (FR-71, NFR-17); rincian diasumsikan, open question 34–42. Path usulan.</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>baru (usulan); ui-mockup/pc-history-costing.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>PG-26</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Hasil dan Pricelist</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>History Price List</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>/history_pricelist</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Halaman CI3 (daftar + modal detail)</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Menampilkan riwayat kejadian Pricelist (Diajukan, Disetujui, Ditolak, Dihitung Ulang, Dirilis) per Produk × varian BOM dengan Price List lama → baru; hanya baca.</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>UC-N20</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Costing, Accounting, Sales, Management: L</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>menu Hasil &amp; Pricelist. Fitur diusulkan (FR-72, NFR-17); rincian diasumsikan, open question 34–42. Path usulan.</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>baru (usulan); ui-mockup/pc-history-pricelist.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/specs/docs/workbook.xlsx
+++ b/specs/docs/workbook.xlsx
@@ -2424,7 +2424,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Costing / Accounting / Sales / Management</t>
+          <t>Pengguna dengan hak akses lihat</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Filter: produk, Product Category, periode, sumber perubahan; pilihan catatan riwayat untuk melihat detail snapshot</t>
+          <t>Filter: produk, Product Category, periode, sumber perubahan; pilihan catatan riwayat untuk melihat detail snapshot; tombol Ekspor Excel</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>FR-71, NFR-17 (diusulkan; rincian diasumsikan, mohon konfirmasi OQ 34–42). 1) Setiap kali perubahan master, rate, atau input costing membuat Bottom Price suatu Produk × varian BOM berubah, sistem menyimpan satu catatan riwayat per Produk × varian BOM (langkah otomatis, tanpa aktor): waktu, pengguna yang mengubah, sumber perubahan (master/rate yang diubah, nilai lama → baru), Bottom Price lama → baru (Rp/Meter dan Rp/Kg), snapshot komponen costing lama dan baru, dan Rate Extra Margin aktif. 2) Pengguna membuka halaman History Costing. 3) Pengguna menyaring menurut produk, Product Category, periode, dan sumber perubahan. 4) Pengguna membuka detail untuk melihat snapshot komponen lama dan baru. Riwayat hanya baca (tidak dapat diubah atau dihapus), dan terpisah dari Notifikasi Bottom Price (UC-N18): notifikasi untuk Sales meninjau, riwayat untuk audit. (Permintaan user 2026-10-21.)</t>
+          <t>FR-71, NFR-17 (dikonfirmasi user 2026-10-21, OQ 34–40; tafsiran terbuka OQ 43–47). 1) Setiap kali costing diperbarui dan hasilnya berubah (Bottom Price atau komponen costing suatu Produk × varian BOM berubah karena perubahan master, rate, atau input costing), sistem menyimpan satu catatan riwayat per Produk × varian BOM (langkah otomatis, tanpa aktor, lewat write_log() sehingga juga tampil di Activity Log): waktu, pengguna yang mengubah, sumber perubahan (master/rate yang diubah, nilai lama → baru), Bottom Price lama → baru (Rp/Meter dan Rp/Kg), snapshot komponen costing lama dan baru, dan Rate Extra Margin aktif. Persetujuan perubahan Rate Extra Margin oleh GM dan Draft Pricelist tidak dicatat. 2) Pengguna dengan hak akses lihat membuka halaman History Costing (menampilkan 12 bulan terakhir; riwayat lewat 1 tahun dipindahkan ke backup data, bukan dihapus). 3) Pengguna menyaring menurut produk, Product Category, periode, dan sumber perubahan. 4) Pengguna membuka detail untuk melihat snapshot komponen lama dan baru. 5) Pengguna dapat mengekspor hasil (sesuai filter) ke Excel. Riwayat hanya baca (tidak dapat diubah atau dihapus), dan terpisah dari Notifikasi Bottom Price (UC-N18): notifikasi untuk Sales meninjau, riwayat untuk audit. (Permintaan dan jawaban user 2026-10-21.)</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Daftar riwayat perubahan Bottom Price dengan detail snapshot komponen lama dan baru</t>
+          <t>Daftar riwayat perubahan Bottom Price (12 bulan terakhir) dengan detail snapshot komponen lama dan baru; hasil dapat diekspor ke Excel</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Costing / Accounting / Sales / Management</t>
+          <t>Pengguna dengan hak akses lihat</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Filter: produk, Product Category, periode, kejadian; pilihan catatan riwayat untuk melihat detail</t>
+          <t>Filter: produk, Product Category, periode, kejadian; pilihan catatan riwayat untuk melihat detail; tombol Ekspor Excel</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>FR-72, NFR-17 (diusulkan; rincian diasumsikan, mohon konfirmasi OQ 34–42; terhubung ke FR-58 dan FR-67). 1) Setiap kejadian pada Pricelist disimpan per Produk × varian BOM (langkah otomatis, tanpa aktor): Diajukan, Disetujui (Approved), Ditolak (Rejected, beserta alasan), Dihitung Ulang (kembali ke Draft), atau Dirilis ke Product Catalog; dengan nomor Pricelist, status, waktu, pengguna, Price List lama → baru (Rp/Meter dan Rp/Kg), Bottom Price dan Rate Extra Margin saat itu, serta catatan atau alasan. 2) Pengguna membuka halaman History Price List. 3) Pengguna menyaring menurut produk, Product Category, periode, dan kejadian. 4) Pengguna melihat perubahan Price List lama → baru. Riwayat hanya baca (tidak dapat diubah atau dihapus). (Permintaan user 2026-10-21.)</t>
+          <t>FR-72, NFR-17 (dikonfirmasi user 2026-10-21, OQ 34–40; tafsiran terbuka OQ 44–47; terhubung ke FR-58 dan FR-67). 1) Setiap kali sebuah Pricelist Disetujui (Approved) oleh Management dan menjadi harga terbaru, sistem menyimpan satu catatan riwayat per Produk × varian BOM (langkah otomatis, tanpa aktor, lewat write_log() sehingga juga tampil di Activity Log): nomor Pricelist, waktu, pengguna (penyetuju), Price List lama (Price List terakhir yang disetujui untuk produk/varian itu) → baru (Rp/Meter dan Rp/Kg), Bottom Price dan Rate Extra Margin saat itu, serta catatan. Draft, Diajukan, Ditolak, Dihitung Ulang, dan persetujuan Rate Extra Margin tidak dicatat; apakah rilis ke Product Catalog dicatat: OQ 44. 2) Pengguna dengan hak akses lihat membuka halaman History Price List (12 bulan terakhir; lewat 1 tahun dipindahkan ke backup data). 3) Pengguna menyaring menurut produk, Product Category, periode, dan kejadian. 4) Pengguna melihat perubahan Price List lama → baru. 5) Pengguna dapat mengekspor hasil (sesuai filter) ke Excel. Riwayat hanya baca (tidak dapat diubah atau dihapus). (Permintaan dan jawaban user 2026-10-21.)</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Daftar riwayat kejadian Pricelist per Produk × varian BOM dengan Price List lama dan baru</t>
+          <t>Daftar riwayat Pricelist yang disetujui per Produk × varian BOM (12 bulan terakhir) dengan Price List lama dan baru; hasil dapat diekspor ke Excel</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -2574,7 +2574,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D199"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="28" customWidth="1" style="1" min="1" max="1"/>
@@ -3565,156 +3565,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3726,7 +3576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K119"/>
+  <dimension ref="A1:K89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5195,7 +5045,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Menampilkan riwayat perubahan Bottom Price per Produk × varian BOM (sumber perubahan, nilai lama → baru, snapshot komponen) untuk audit; hanya baca.</t>
+          <t>Menampilkan riwayat perubahan Bottom Price per Produk × varian BOM saat costing diperbarui (sumber perubahan, nilai lama → baru, snapshot komponen) untuk audit; hanya baca; ekspor Excel.</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -5205,7 +5055,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Costing, Accounting, Sales, Management: L</t>
+          <t>Pengguna dengan hak akses lihat</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -5215,7 +5065,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>menu Hasil &amp; Pricelist. Fitur diusulkan (FR-71, NFR-17); rincian diasumsikan, open question 34–42. Path usulan.</t>
+          <t>menu Hasil &amp; Pricelist. Fitur diusulkan (FR-71, NFR-17); OQ 34–40 terjawab 2026-10-21, tafsiran OQ 43–47. Hanya baca; menampilkan 12 bulan terakhir (lebih lama di backup data); pencatatan lewat write_log (Activity Log); persetujuan Extra Margin tidak dicatat. Path usulan.</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
@@ -5252,7 +5102,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Menampilkan riwayat kejadian Pricelist (Diajukan, Disetujui, Ditolak, Dihitung Ulang, Dirilis) per Produk × varian BOM dengan Price List lama → baru; hanya baca.</t>
+          <t>Menampilkan riwayat Pricelist yang sudah Disetujui per Produk × varian BOM dengan Price List lama → baru; hanya baca; ekspor Excel.</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -5262,7 +5112,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Costing, Accounting, Sales, Management: L</t>
+          <t>Pengguna dengan hak akses lihat</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -5272,7 +5122,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>menu Hasil &amp; Pricelist. Fitur diusulkan (FR-72, NFR-17); rincian diasumsikan, open question 34–42. Path usulan.</t>
+          <t>menu Hasil &amp; Pricelist. Fitur diusulkan (FR-72, NFR-17); OQ 34–40 terjawab 2026-10-21, tafsiran OQ 44–47. Hanya baca; dicatat hanya saat Disetujui (Draft dan Extra Margin tidak dicatat); 12 bulan terakhir (lebih lama di backup data); pencatatan lewat write_log (Activity Log). Path usulan.</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
@@ -5343,36 +5193,6 @@
     <row r="87"/>
     <row r="88"/>
     <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/specs/docs/workbook.xlsx
+++ b/specs/docs/workbook.xlsx
@@ -2424,7 +2424,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Pengguna dengan hak akses lihat</t>
+          <t>Pengguna dengan hak akses View (ekspor Excel: Manage)</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>FR-71, NFR-17 (dikonfirmasi user 2026-10-21, OQ 34–40; tafsiran terbuka OQ 43–47). 1) Setiap kali costing diperbarui dan hasilnya berubah (Bottom Price atau komponen costing suatu Produk × varian BOM berubah karena perubahan master, rate, atau input costing), sistem menyimpan satu catatan riwayat per Produk × varian BOM (langkah otomatis, tanpa aktor, lewat write_log() sehingga juga tampil di Activity Log): waktu, pengguna yang mengubah, sumber perubahan (master/rate yang diubah, nilai lama → baru), Bottom Price lama → baru (Rp/Meter dan Rp/Kg), snapshot komponen costing lama dan baru, dan Rate Extra Margin aktif. Persetujuan perubahan Rate Extra Margin oleh GM dan Draft Pricelist tidak dicatat. 2) Pengguna dengan hak akses lihat membuka halaman History Costing (menampilkan 12 bulan terakhir; riwayat lewat 1 tahun dipindahkan ke backup data, bukan dihapus). 3) Pengguna menyaring menurut produk, Product Category, periode, dan sumber perubahan. 4) Pengguna membuka detail untuk melihat snapshot komponen lama dan baru. 5) Pengguna dapat mengekspor hasil (sesuai filter) ke Excel. Riwayat hanya baca (tidak dapat diubah atau dihapus), dan terpisah dari Notifikasi Bottom Price (UC-N18): notifikasi untuk Sales meninjau, riwayat untuk audit. (Permintaan dan jawaban user 2026-10-21.)</t>
+          <t>FR-71, NFR-17 (dikonfirmasi user 2026-10-21, OQ 34–40 dan 43–47; terbuka OQ 41, 42, 48, 49). 1) Pemicu utama: aksi Update Costing (tombol di Simulasi Costing). Setiap kali Update Costing dijalankan dan hasil costing berbeda dari hasil costing terakhir yang tersimpan (Bottom Price atau komponen costing suatu Produk × varian BOM berubah karena perubahan master, rate, atau input costing), sistem menyimpan satu catatan riwayat per Produk × varian BOM (langkah otomatis, tanpa aktor, lewat write_log() sehingga juga tampil di Activity Log): waktu, pengguna yang mengubah, sumber perubahan (master/rate yang berubah sejak Update Costing sebelumnya, nilai lama → baru), Bottom Price lama → baru (Rp/Meter dan Rp/Kg), snapshot komponen costing lama dan baru, dan Rate Extra Margin aktif. Persetujuan perubahan Rate Extra Margin oleh GM dan Draft Pricelist tidak dicatat. 2) Pengguna dengan hak akses lihat membuka halaman History Costing (menampilkan 12 bulan terakhir; riwayat lewat 1 tahun dipindahkan ke backup data, bukan dihapus). 3) Pengguna menyaring menurut produk, Product Category, periode, dan sumber perubahan. 4) Pengguna membuka detail untuk melihat snapshot komponen lama dan baru. 5) Pengguna dengan hak akses Manage dapat mengekspor hasil (sesuai filter) ke Excel; ekspor tidak mencakup backup. Riwayat hanya baca (tidak dapat diubah atau dihapus), dan terpisah dari Notifikasi Bottom Price (UC-N18): notifikasi untuk Sales meninjau, riwayat untuk audit. (Permintaan dan jawaban user 2026-10-21.)</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Pengguna dengan hak akses lihat</t>
+          <t>Pengguna dengan hak akses View (ekspor Excel: Manage)</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Filter: produk, Product Category, periode, kejadian; pilihan catatan riwayat untuk melihat detail; tombol Ekspor Excel</t>
+          <t>Filter: produk, Product Category, periode; pilihan catatan riwayat untuk melihat detail; tombol Ekspor Excel</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>FR-72, NFR-17 (dikonfirmasi user 2026-10-21, OQ 34–40; tafsiran terbuka OQ 44–47; terhubung ke FR-58 dan FR-67). 1) Setiap kali sebuah Pricelist Disetujui (Approved) oleh Management dan menjadi harga terbaru, sistem menyimpan satu catatan riwayat per Produk × varian BOM (langkah otomatis, tanpa aktor, lewat write_log() sehingga juga tampil di Activity Log): nomor Pricelist, waktu, pengguna (penyetuju), Price List lama (Price List terakhir yang disetujui untuk produk/varian itu) → baru (Rp/Meter dan Rp/Kg), Bottom Price dan Rate Extra Margin saat itu, serta catatan. Draft, Diajukan, Ditolak, Dihitung Ulang, dan persetujuan Rate Extra Margin tidak dicatat; apakah rilis ke Product Catalog dicatat: OQ 44. 2) Pengguna dengan hak akses lihat membuka halaman History Price List (12 bulan terakhir; lewat 1 tahun dipindahkan ke backup data). 3) Pengguna menyaring menurut produk, Product Category, periode, dan kejadian. 4) Pengguna melihat perubahan Price List lama → baru. 5) Pengguna dapat mengekspor hasil (sesuai filter) ke Excel. Riwayat hanya baca (tidak dapat diubah atau dihapus). (Permintaan dan jawaban user 2026-10-21.)</t>
+          <t>FR-72, NFR-17 (dikonfirmasi user 2026-10-21, OQ 34–40 dan 44–47; terbuka OQ 41, 42, 48, 49; terhubung ke FR-58 dan FR-67). 1) Setiap kali sebuah Pricelist Disetujui (Approved) oleh Management dan menjadi harga terbaru, sistem menyimpan satu catatan riwayat per Produk × varian BOM (langkah otomatis, tanpa aktor, lewat write_log() sehingga juga tampil di Activity Log): nomor Pricelist, waktu, pengguna (penyetuju), Price List lama (Price List terakhir yang disetujui untuk produk/varian itu) → baru (Rp/Meter dan Rp/Kg), Bottom Price dan Rate Extra Margin saat itu, serta catatan. Draft, Diajukan, Ditolak, Dihitung Ulang, dan persetujuan Rate Extra Margin tidak dicatat; rilis ke Product Catalog tidak dicatat (cukup Approval Pricelist yang menetapkan Pricelist terbaru). 2) Pengguna dengan hak akses lihat membuka halaman History Price List (12 bulan terakhir; lewat 1 tahun dipindahkan ke backup data). 3) Pengguna menyaring menurut produk, Product Category, dan periode. 4) Pengguna melihat perubahan Price List lama → baru. 5) Pengguna dengan hak akses Manage dapat mengekspor hasil (sesuai filter) ke Excel; ekspor tidak mencakup backup. Riwayat hanya baca (tidak dapat diubah atau dihapus). (Permintaan dan jawaban user 2026-10-21.)</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Pengguna dengan hak akses lihat</t>
+          <t>View: lihat · Manage: ekspor Excel dan akses backup (hak akses terpisah per halaman, diatur di program; hak akses backup = tafsiran/asumsi, OQ 49)</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>menu Hasil &amp; Pricelist. Fitur diusulkan (FR-71, NFR-17); OQ 34–40 terjawab 2026-10-21, tafsiran OQ 43–47. Hanya baca; menampilkan 12 bulan terakhir (lebih lama di backup data); pencatatan lewat write_log (Activity Log); persetujuan Extra Margin tidak dicatat. Path usulan.</t>
+          <t>menu Hasil &amp; Pricelist. Fitur diusulkan (FR-71, NFR-17); OQ 34–40 dan 43–47 terjawab 2026-10-21; terbuka OQ 41, 42, 48, 49. Pemicu = tombol Update Costing. Ekspor Excel tidak mencakup backup. Hanya baca; menampilkan 12 bulan terakhir (lebih lama di backup data); pencatatan lewat write_log (Activity Log); persetujuan Extra Margin tidak dicatat. Path usulan.</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Pengguna dengan hak akses lihat</t>
+          <t>View: lihat · Manage: ekspor Excel dan akses backup (hak akses terpisah per halaman, diatur di program; hak akses backup = tafsiran/asumsi, OQ 49)</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>menu Hasil &amp; Pricelist. Fitur diusulkan (FR-72, NFR-17); OQ 34–40 terjawab 2026-10-21, tafsiran OQ 44–47. Hanya baca; dicatat hanya saat Disetujui (Draft dan Extra Margin tidak dicatat); 12 bulan terakhir (lebih lama di backup data); pencatatan lewat write_log (Activity Log). Path usulan.</t>
+          <t>menu Hasil &amp; Pricelist. Fitur diusulkan (FR-72, NFR-17); OQ 34–40 dan 44–47 terjawab 2026-10-21; terbuka OQ 41, 42, 48, 49. Rilis katalog tidak dicatat. Ekspor Excel tidak mencakup backup. Hanya baca; dicatat hanya saat Disetujui (Draft dan Extra Margin tidak dicatat); 12 bulan terakhir (lebih lama di backup data); pencatatan lewat write_log (Activity Log). Path usulan.</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">

--- a/specs/docs/workbook.xlsx
+++ b/specs/docs/workbook.xlsx
@@ -2392,7 +2392,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>FR-68, FR-69, FR-70, NFR-16 (diusulkan; seluruh rincian dikonfirmasi user 2026-10-21 — OQ 25–33). 1) Sistem membandingkan Bottom Price (Rp/Meter dan Rp/Kg) tiap Produk × varian BOM dengan baseline setiap kali costing dihitung; bila berbeda (naik atau turun, apa pun penyebabnya) sistem membuat notifikasi berstatus Belum Ditinjau (langkah otomatis, tanpa aktor). 2) Sales (Staf Sales atau Sales Manager) membuka dashboard notifikasi; notifikasi dikelompokkan per Product Category dan jumlah yang belum ditinjau tampil sebagai lencana di menu. 3) Sales membandingkan Bottom Price lama dan baru, selisih (Rp dan %), komponen yang berubah, Rate Extra Margin aktif, harga jual saat ini terhadap Price List baru bila rate lama dipertahankan. 4) Sales memilih: a) Ajukan Rate Extra Margin Baru (hanya Sales Manager; hak akses diatur per pengguna di program): membuka pengajuan UC-12 untuk Product Category itu, lalu GM memutuskan di UC-16 (FR-67); status Diajukan Extra Margin Baru dan terhubung ke pengajuan; b) Tidak Perlu Diubah (catatan opsional): status Tidak Perlu Diubah. 5) Kedua keputusan mencatat peninjau, waktu, dan catatan, ditulis ke log, dan menggeser baseline ke Bottom Price baru. Sistem tidak mengubah rate, Pricelist, atau Katalog secara otomatis. Semua Sales dapat meninjau; kanal hanya dashboard (tanpa email/WhatsApp) dan tanpa batas waktu tinjau; ambang: perubahan sekecil apa pun (≥ Rp0,01). Di luar scope: persetujuan diskon Quotation. (Permintaan user 2026-10-21; terkait BPMN To Be Sales D01, gateway "Perlu Perubahan Margin?".)</t>
+          <t>FR-68, FR-69, FR-70, NFR-16 (diusulkan; seluruh rincian dikonfirmasi user 2026-10-21 — OQ 25–33 dan 48). 1) Sistem membandingkan Bottom Price (Rp/Meter dan Rp/Kg) tiap Produk × varian BOM dengan baseline setiap kali Update Costing dijalankan (tombol di Simulasi Costing, oleh pengguna yang menjalankan Update Costing; pemicu yang sama dengan History Costing, OQ 48); bila berbeda (naik atau turun, apa pun penyebabnya) sistem membuat notifikasi berstatus Belum Ditinjau (langkah otomatis setelah Update Costing). 2) Sales (Staf Sales atau Sales Manager) membuka dashboard notifikasi; notifikasi dikelompokkan per Product Category dan jumlah yang belum ditinjau tampil sebagai lencana di menu. 3) Sales membandingkan Bottom Price lama dan baru, selisih (Rp dan %), komponen yang berubah, Rate Extra Margin aktif, harga jual saat ini terhadap Price List baru bila rate lama dipertahankan. 4) Sales memilih: a) Ajukan Rate Extra Margin Baru (hanya Sales Manager; hak akses diatur per pengguna di program): membuka pengajuan UC-12 untuk Product Category itu, lalu GM memutuskan di UC-16 (FR-67); status Diajukan Extra Margin Baru dan terhubung ke pengajuan; b) Tidak Perlu Diubah (catatan opsional): status Tidak Perlu Diubah. 5) Kedua keputusan mencatat peninjau, waktu, dan catatan, ditulis ke log, dan menggeser baseline ke Bottom Price baru. Sistem tidak mengubah rate, Pricelist, atau Katalog secara otomatis. Semua Sales dapat meninjau; kanal hanya dashboard (tanpa email/WhatsApp) dan tanpa batas waktu tinjau; ambang: perubahan sekecil apa pun (≥ Rp0,01). Di luar scope: persetujuan diskon Quotation. (Permintaan user 2026-10-21; terkait BPMN To Be Sales D01, gateway "Perlu Perubahan Margin?".)</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>FR-71, NFR-17 (dikonfirmasi user 2026-10-21, OQ 34–40 dan 43–47; terbuka OQ 41, 42, 48, 49). 1) Pemicu utama: aksi Update Costing (tombol di Simulasi Costing). Setiap kali Update Costing dijalankan dan hasil costing berbeda dari hasil costing terakhir yang tersimpan (Bottom Price atau komponen costing suatu Produk × varian BOM berubah karena perubahan master, rate, atau input costing), sistem menyimpan satu catatan riwayat per Produk × varian BOM (langkah otomatis, tanpa aktor, lewat write_log() sehingga juga tampil di Activity Log): waktu, pengguna yang mengubah, sumber perubahan (master/rate yang berubah sejak Update Costing sebelumnya, nilai lama → baru), Bottom Price lama → baru (Rp/Meter dan Rp/Kg), snapshot komponen costing lama dan baru, dan Rate Extra Margin aktif. Persetujuan perubahan Rate Extra Margin oleh GM dan Draft Pricelist tidak dicatat. 2) Pengguna dengan hak akses lihat membuka halaman History Costing (menampilkan 12 bulan terakhir; riwayat lewat 1 tahun dipindahkan ke backup data, bukan dihapus). 3) Pengguna menyaring menurut produk, Product Category, periode, dan sumber perubahan. 4) Pengguna membuka detail untuk melihat snapshot komponen lama dan baru. 5) Pengguna dengan hak akses Manage dapat mengekspor hasil (sesuai filter) ke Excel; ekspor tidak mencakup backup. Riwayat hanya baca (tidak dapat diubah atau dihapus), dan terpisah dari Notifikasi Bottom Price (UC-N18): notifikasi untuk Sales meninjau, riwayat untuk audit. (Permintaan dan jawaban user 2026-10-21.)</t>
+          <t>FR-71, NFR-17 (dikonfirmasi user 2026-10-21, OQ 34–40 dan 43–49; terbuka OQ 41, 42). 1) Pemicu utama: aksi Update Costing (tombol di Simulasi Costing). Setiap kali Update Costing dijalankan dan hasil costing berbeda dari hasil costing terakhir yang tersimpan (Bottom Price atau komponen costing suatu Produk × varian BOM berubah karena perubahan master, rate, atau input costing), sistem menyimpan satu catatan riwayat per Produk × varian BOM (langkah otomatis, tanpa aktor, lewat write_log() sehingga juga tampil di Activity Log): waktu, pengguna yang mengubah, sumber perubahan (master/rate yang berubah sejak Update Costing sebelumnya, nilai lama → baru), Bottom Price lama → baru (Rp/Meter dan Rp/Kg), snapshot komponen costing lama dan baru, dan Rate Extra Margin aktif. Persetujuan perubahan Rate Extra Margin oleh GM dan Draft Pricelist tidak dicatat. 2) Pengguna dengan hak akses lihat membuka halaman History Costing (menampilkan 12 bulan terakhir; riwayat lewat 1 tahun dipindahkan ke backup data, bukan dihapus). 3) Pengguna menyaring menurut produk, Product Category, periode, dan sumber perubahan. 4) Pengguna membuka detail untuk melihat snapshot komponen lama dan baru. 5) Pengguna dengan hak akses Manage dapat mengekspor hasil (sesuai filter) ke Excel; ekspor tidak mencakup backup. Riwayat hanya baca (tidak dapat diubah atau dihapus), dan terpisah dari Notifikasi Bottom Price (UC-N18): notifikasi untuk Sales meninjau, riwayat untuk audit. (Permintaan dan jawaban user 2026-10-21.)</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>FR-72, NFR-17 (dikonfirmasi user 2026-10-21, OQ 34–40 dan 44–47; terbuka OQ 41, 42, 48, 49; terhubung ke FR-58 dan FR-67). 1) Setiap kali sebuah Pricelist Disetujui (Approved) oleh Management dan menjadi harga terbaru, sistem menyimpan satu catatan riwayat per Produk × varian BOM (langkah otomatis, tanpa aktor, lewat write_log() sehingga juga tampil di Activity Log): nomor Pricelist, waktu, pengguna (penyetuju), Price List lama (Price List terakhir yang disetujui untuk produk/varian itu) → baru (Rp/Meter dan Rp/Kg), Bottom Price dan Rate Extra Margin saat itu, serta catatan. Draft, Diajukan, Ditolak, Dihitung Ulang, dan persetujuan Rate Extra Margin tidak dicatat; rilis ke Product Catalog tidak dicatat (cukup Approval Pricelist yang menetapkan Pricelist terbaru). 2) Pengguna dengan hak akses lihat membuka halaman History Price List (12 bulan terakhir; lewat 1 tahun dipindahkan ke backup data). 3) Pengguna menyaring menurut produk, Product Category, dan periode. 4) Pengguna melihat perubahan Price List lama → baru. 5) Pengguna dengan hak akses Manage dapat mengekspor hasil (sesuai filter) ke Excel; ekspor tidak mencakup backup. Riwayat hanya baca (tidak dapat diubah atau dihapus). (Permintaan dan jawaban user 2026-10-21.)</t>
+          <t>FR-72, NFR-17 (dikonfirmasi user 2026-10-21, OQ 34–40 dan 44–49; terbuka OQ 41, 42; terhubung ke FR-58 dan FR-67). 1) Setiap kali sebuah Pricelist Disetujui (Approved) oleh Management dan menjadi harga terbaru, sistem menyimpan satu catatan riwayat per Produk × varian BOM (langkah otomatis, tanpa aktor, lewat write_log() sehingga juga tampil di Activity Log): nomor Pricelist, waktu, pengguna (penyetuju), Price List lama (Price List terakhir yang disetujui untuk produk/varian itu) → baru (Rp/Meter dan Rp/Kg), Bottom Price dan Rate Extra Margin saat itu, serta catatan. Draft, Diajukan, Ditolak, Dihitung Ulang, dan persetujuan Rate Extra Margin tidak dicatat; rilis ke Product Catalog tidak dicatat (cukup Approval Pricelist yang menetapkan Pricelist terbaru). 2) Pengguna dengan hak akses lihat membuka halaman History Price List (12 bulan terakhir; lewat 1 tahun dipindahkan ke backup data). 3) Pengguna menyaring menurut produk, Product Category, dan periode. 4) Pengguna melihat perubahan Price List lama → baru. 5) Pengguna dengan hak akses Manage dapat mengekspor hasil (sesuai filter) ke Excel; ekspor tidak mencakup backup. Riwayat hanya baca (tidak dapat diubah atau dihapus). (Permintaan dan jawaban user 2026-10-21.)</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>menu Hasil &amp; Pricelist; lencana jumlah notifikasi Belum Ditinjau di menu. Fitur diusulkan (FR-68–FR-70, NFR-16); rincian diasumsikan, open question 25–33 terjawab 2026-10-21. Path usulan.</t>
+          <t>menu Hasil &amp; Pricelist; lencana jumlah notifikasi Belum Ditinjau di menu. Fitur diusulkan (FR-68–FR-70, NFR-16); rincian diasumsikan, open question 25–33 dan 48 terjawab 2026-10-21 (pemicu deteksi = Update Costing). Path usulan.</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>View: lihat · Manage: ekspor Excel dan akses backup (hak akses terpisah per halaman, diatur di program; hak akses backup = tafsiran/asumsi, OQ 49)</t>
+          <t>View: lihat · Manage: ekspor Excel dan akses backup (hak akses terpisah per halaman, diatur di program; hak akses backup = Manage, dikonfirmasi user 2026-10-21, OQ 49)</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>menu Hasil &amp; Pricelist. Fitur diusulkan (FR-71, NFR-17); OQ 34–40 dan 43–47 terjawab 2026-10-21; terbuka OQ 41, 42, 48, 49. Pemicu = tombol Update Costing. Ekspor Excel tidak mencakup backup. Hanya baca; menampilkan 12 bulan terakhir (lebih lama di backup data); pencatatan lewat write_log (Activity Log); persetujuan Extra Margin tidak dicatat. Path usulan.</t>
+          <t>menu Hasil &amp; Pricelist. Fitur diusulkan (FR-71, NFR-17); OQ 34–40 dan 43–47 terjawab 2026-10-21; terbuka OQ 41, 42; OQ 48 dan 49 terjawab 2026-10-21. Pemicu = tombol Update Costing. Ekspor Excel tidak mencakup backup. Hanya baca; menampilkan 12 bulan terakhir (lebih lama di backup data); pencatatan lewat write_log (Activity Log); persetujuan Extra Margin tidak dicatat. Path usulan.</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>View: lihat · Manage: ekspor Excel dan akses backup (hak akses terpisah per halaman, diatur di program; hak akses backup = tafsiran/asumsi, OQ 49)</t>
+          <t>View: lihat · Manage: ekspor Excel dan akses backup (hak akses terpisah per halaman, diatur di program; hak akses backup = Manage, dikonfirmasi user 2026-10-21, OQ 49)</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>menu Hasil &amp; Pricelist. Fitur diusulkan (FR-72, NFR-17); OQ 34–40 dan 44–47 terjawab 2026-10-21; terbuka OQ 41, 42, 48, 49. Rilis katalog tidak dicatat. Ekspor Excel tidak mencakup backup. Hanya baca; dicatat hanya saat Disetujui (Draft dan Extra Margin tidak dicatat); 12 bulan terakhir (lebih lama di backup data); pencatatan lewat write_log (Activity Log). Path usulan.</t>
+          <t>menu Hasil &amp; Pricelist. Fitur diusulkan (FR-72, NFR-17); OQ 34–40 dan 44–47 terjawab 2026-10-21; terbuka OQ 41, 42; OQ 48 dan 49 terjawab 2026-10-21. Rilis katalog tidak dicatat. Ekspor Excel tidak mencakup backup. Hanya baca; dicatat hanya saat Disetujui (Draft dan Extra Margin tidak dicatat); 12 bulan terakhir (lebih lama di backup data); pencatatan lewat write_log (Activity Log). Path usulan.</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">

--- a/specs/docs/workbook.xlsx
+++ b/specs/docs/workbook.xlsx
@@ -799,7 +799,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>FR-05 dan FR-06 (bagian Operator): Setelah unpacking, Operator melakukan Cek Kondisi Coil — pemeriksaan fisik (Manual task, dikecualikan dari UC, tanpa keterlibatan sistem). Bila hasilnya 'Tidak sesuai', Operator menginput Laporan Ketidaksesuaian Material ke sistem, yang kemudian dikirim ke Claim Material (proses lain, di luar Modul Produksi).</t>
+          <t>FR-05 dan FR-06 (bagian Operator): Setelah unpacking, Operator melakukan Cek Kondisi Coil — pemeriksaan fisik (Manual task, dikecualikan dari UC, tanpa keterlibatan sistem). Bila hasilnya 'Tidak sesuai', Operator menginput Laporan Ketidaksesuaian Material ke sistem, yang kemudian dikirim ke Claim Material (proses lain, di luar Modul Produksi). [2026-10-26, FR-48 direvisi/FR-74] Saat Add SPK, setelah memilih produk, pengguna memilih varian BOM (uniq_id); dibawa ke item laporan (OQ 50-55).</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -1236,7 +1236,7 @@
       <c r="F12" s="3" t="inlineStr">
         <is>
           <t>FR-24: Accounting melakukan Posting Jurnal Produksi ke GL Interface berdasarkan Nilai Material dan HPP hasil FR-19 s.d. FR-23, mencakup jurnal: KW1, KW2, Scrap, Inventory, Hutang Biaya Proses, Hutang Scrap, dan Hutang Koordinasi.
-Field-level dari ERD revisi klien (Rev.2, menggantikan Rev.1), bukan UC terpisah: FR-34 - komponen biaya HPP per item (tujuh komponen x *_cost_per_pcs/*_cost_total, plus total_hpp_item) pada production_report_items, dibedakan oleh category_type; menggantikan FR-28. FR-35 - scrap per baris (scrap_type, qty, berat_total, berat_material_plat) pada production_report_scraps; menggantikan FR-27. Total HPP keseluruhan pada header production_reports (total_hpp_keseluruhan, FR-32). Catatan: pemisahan 80%/20% (KW 2) dan 40%/60% (scrap) belum punya kolom di Rev.2 (open question, belum dikonfirmasi).</t>
+Field-level dari ERD revisi klien (Rev.2, menggantikan Rev.1), bukan UC terpisah: FR-34 - komponen biaya HPP per item (tujuh komponen x *_cost_per_pcs/*_cost_total, plus total_hpp_item) pada production_report_items, dibedakan oleh category_type; menggantikan FR-28. FR-35 - scrap per baris (scrap_type, qty, berat_total, berat_material_plat) pada production_report_scraps; menggantikan FR-27. Total HPP keseluruhan pada header production_reports (total_hpp_keseluruhan, FR-32). Catatan: pemisahan 80%/20% (KW 2) dan 40%/60% (scrap) belum punya kolom di Rev.2 (open question, belum dikonfirmasi). [2026-10-26, FR-48 direvisi/FR-74] Komponen HPP selain Material = Rp/Kg Hasil Costing varian BOM x berat per pcs (bukan Master Rate rate.html).</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1501,7 +1501,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="10" customWidth="1" style="1" min="1" max="1"/>
@@ -2505,64 +2505,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3576,7 +3518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K89"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3868,7 +3810,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>menu Produksi (Daftar SPK, Input Produksi). Satu aktor, satu sitting, satu entitas (production_reports); 11 UC dalam satu halaman bersektor. Modul sudah ada (index, ajax_spk_list, create, ajax_get_coils, save, view).</t>
+          <t>menu Produksi (Daftar SPK, Input Produksi). Satu aktor, satu sitting, satu entitas (production_reports); 11 UC dalam satu halaman bersektor. Modul sudah ada (index, ajax_spk_list, create, ajax_get_coils, save, view). [2026-10-26, FR-48 direvisi/FR-74] Add SPK: pilih varian BOM setelah produk.</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -3925,7 +3867,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>menu Produksi (HPP). Modul gl_interface sudah ada (index, data, detail, view, post, post_batch).</t>
+          <t>menu Produksi (HPP). Modul gl_interface sudah ada (index, data, detail, view, post, post_batch). [2026-10-26, FR-48 direvisi/FR-74] Rate komponen biaya dari Hasil Costing (pc-simulasi) varian BOM SPK; rate.html tidak lagi dipakai.</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -5131,68 +5073,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/specs/docs/workbook.xlsx
+++ b/specs/docs/workbook.xlsx
@@ -799,7 +799,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>FR-05 dan FR-06 (bagian Operator): Setelah unpacking, Operator melakukan Cek Kondisi Coil — pemeriksaan fisik (Manual task, dikecualikan dari UC, tanpa keterlibatan sistem). Bila hasilnya 'Tidak sesuai', Operator menginput Laporan Ketidaksesuaian Material ke sistem, yang kemudian dikirim ke Claim Material (proses lain, di luar Modul Produksi). [2026-10-26, FR-48 direvisi/FR-74] Saat Add SPK, setelah memilih produk, pengguna memilih varian BOM (uniq_id); dibawa ke item laporan (OQ 50-55).</t>
+          <t>FR-05 dan FR-06 (bagian Operator): Setelah unpacking, Operator melakukan Cek Kondisi Coil — pemeriksaan fisik (Manual task, dikecualikan dari UC, tanpa keterlibatan sistem). Bila hasilnya 'Tidak sesuai', Operator menginput Laporan Ketidaksesuaian Material ke sistem, yang kemudian dikirim ke Claim Material (proses lain, di luar Modul Produksi). [2026-10-26, FR-48 direvisi/FR-74] Saat Add SPK, setelah memilih produk, pengguna memilih varian BOM (uniq_id); dibawa ke item laporan (OQ 50-55). [2026-10-26, OQ 50/51/53/55 dijawab] SPK ditolak bila produk tanpa varian BOM atau Hasil Costing belum lengkap; varian per produk; varian dapat diubah selama SPK belum diinput laporan produksinya; SPK dibuat di modul Production Planning (eksternal).</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>menu Produksi (Daftar SPK, Input Produksi). Satu aktor, satu sitting, satu entitas (production_reports); 11 UC dalam satu halaman bersektor. Modul sudah ada (index, ajax_spk_list, create, ajax_get_coils, save, view). [2026-10-26, FR-48 direvisi/FR-74] Add SPK: pilih varian BOM setelah produk.</t>
+          <t>menu Produksi (Daftar SPK, Input Produksi). Satu aktor, satu sitting, satu entitas (production_reports); 11 UC dalam satu halaman bersektor. Modul sudah ada (index, ajax_spk_list, create, ajax_get_coils, save, view). [2026-10-26, FR-48 direvisi/FR-74] Add SPK: pilih varian BOM setelah produk. [2026-10-26, OQ 50/51/53/55] SPK ditolak bila produk tanpa varian BOM/Hasil Costing lengkap; varian per produk; terkunci setelah laporan produksi diinput; Add SPK di mockup hanya simulasi modul Production Planning (eksternal).</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>menu Produksi (HPP). Modul gl_interface sudah ada (index, data, detail, view, post, post_batch). [2026-10-26, FR-48 direvisi/FR-74] Rate komponen biaya dari Hasil Costing (pc-simulasi) varian BOM SPK; rate.html tidak lagi dipakai.</t>
+          <t>menu Produksi (HPP). Modul gl_interface sudah ada (index, data, detail, view, post, post_batch). [2026-10-26, FR-48 direvisi/FR-74] Rate komponen biaya dari Hasil Costing (pc-simulasi) varian BOM SPK; rate.html (Master Rate lama) dipensiunkan (OQ 54, dijawab user 2026-10-26).</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">

--- a/specs/docs/workbook.xlsx
+++ b/specs/docs/workbook.xlsx
@@ -799,7 +799,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>FR-05 dan FR-06 (bagian Operator): Setelah unpacking, Operator melakukan Cek Kondisi Coil — pemeriksaan fisik (Manual task, dikecualikan dari UC, tanpa keterlibatan sistem). Bila hasilnya 'Tidak sesuai', Operator menginput Laporan Ketidaksesuaian Material ke sistem, yang kemudian dikirim ke Claim Material (proses lain, di luar Modul Produksi). [2026-10-26, FR-48 direvisi/FR-74] Saat Add SPK, setelah memilih produk, pengguna memilih varian BOM (uniq_id); dibawa ke item laporan (OQ 50-55). [2026-10-26, OQ 50/51/53/55 dijawab] SPK ditolak bila produk tanpa varian BOM atau Hasil Costing belum lengkap; varian per produk; varian dapat diubah selama SPK belum diinput laporan produksinya; SPK dibuat di modul Production Planning (eksternal).</t>
+          <t>FR-05 dan FR-06 (bagian Operator): Setelah unpacking, Operator melakukan Cek Kondisi Coil — pemeriksaan fisik (Manual task, dikecualikan dari UC, tanpa keterlibatan sistem). Bila hasilnya 'Tidak sesuai', Operator menginput Laporan Ketidaksesuaian Material ke sistem, yang kemudian dikirim ke Claim Material (proses lain, di luar Modul Produksi). [2026-10-26, FR-48 direvisi/FR-74] Saat Add SPK, setelah memilih produk, pengguna memilih varian BOM (kolom varian_type; label tampilan Varian BOM (varian_type)); dibawa ke item laporan (OQ 50-55). [2026-10-26, OQ 50/51/53/55 dijawab] SPK ditolak bila produk tanpa varian BOM atau Hasil Costing belum lengkap; varian per produk; varian dapat diubah selama SPK belum diinput laporan produksinya; SPK dibuat di modul Production Planning (eksternal). [2026-10-26, varian_type] Item Stok Bebas dan KW 2 pada laporan produksi mengikuti varian BOM yang dipilih di SPK; ERD yang diperbarui = erd-revisi.drawio.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>menu Produksi (Daftar SPK, Input Produksi). Satu aktor, satu sitting, satu entitas (production_reports); 11 UC dalam satu halaman bersektor. Modul sudah ada (index, ajax_spk_list, create, ajax_get_coils, save, view). [2026-10-26, FR-48 direvisi/FR-74] Add SPK: pilih varian BOM setelah produk. [2026-10-26, OQ 50/51/53/55] SPK ditolak bila produk tanpa varian BOM/Hasil Costing lengkap; varian per produk; terkunci setelah laporan produksi diinput; Add SPK di mockup hanya simulasi modul Production Planning (eksternal).</t>
+          <t>menu Produksi (Daftar SPK, Input Produksi). Satu aktor, satu sitting, satu entitas (production_reports); 11 UC dalam satu halaman bersektor. Modul sudah ada (index, ajax_spk_list, create, ajax_get_coils, save, view). [2026-10-26, FR-48 direvisi/FR-74] Add SPK: pilih varian BOM setelah produk (kolom varian_type; label Varian BOM (varian_type)). [2026-10-26, OQ 50/51/53/55] SPK ditolak bila produk tanpa varian BOM/Hasil Costing lengkap; varian per produk; terkunci setelah laporan produksi diinput; Add SPK di mockup hanya simulasi modul Production Planning (eksternal).</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">

--- a/specs/docs/workbook.xlsx
+++ b/specs/docs/workbook.xlsx
@@ -1969,7 +1969,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>FR-41, FR-51. Prasyarat: Master Produk (UC-N05), Master Material (UC-N06), Master Standard Material (UC-N15). 1) Engineering membuka daftar BOM per produk. 2) Engineering menambah varian BOM (Varian Tebal) untuk produk dengan memilih material dari Master Material. 3) Sistem menghitung Berat/Meter (kg/m) = ((Tebal Material − Standar Toleransi) × Lebar Coil × Standar Berat Jenis) + Coating dari Master Standard Material (global; satuan tidak ditampilkan, konversi dikalibrasi 0,14 mm × lebar 1219 × 7,85 ≈ 1,34 kg/m — FR-50) dan menyimpannya pada bom_detail. 4) Sistem membuat No. Uniq ID per varian (mis. Type 001.1) dan mengisi Latest Update dan Updated By. 5) Engineering dapat View, Edit, atau Delete varian. Satu produk boleh memakai beberapa material, tetapi tidak boleh memakai material yang sama dua kali (unik produk + material). (Rev.1 UC-04; BPMN D05: 'Develop BOM Produk berdasarkan Varian Tebal'.)</t>
+          <t>FR-41, FR-51. Prasyarat: Master Produk (UC-N05), Master Material (UC-N06), Master Standard Material (UC-N15). 1) Engineering membuka daftar BOM per produk. 2) Engineering menambah varian BOM (Varian Tebal) untuk produk dengan memilih material dari Master Material. 3) Sistem menghitung Berat/Meter (kg/m) = ((Tebal Material − Standar Toleransi) × Lebar Coil × Standar Berat Jenis) + Coating dari Master Standard Material (global; satuan tidak ditampilkan, konversi dikalibrasi 0,14 mm × lebar 1219 × 7,85 ≈ 1,34 kg/m — FR-50) dan menyimpannya pada ms_bom_detail. 4) Sistem membuat No. Uniq ID per varian (mis. Type 001.1) dan mengisi Latest Update dan Updated By. 5) Engineering dapat View, Edit, atau Delete varian. Satu produk boleh memakai beberapa material, tetapi tidak boleh memakai material yang sama dua kali (unik produk + material). (Rev.1 UC-04; BPMN D05: 'Develop BOM Produk berdasarkan Varian Tebal'.)</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>bom_header, bom_detail, product_lvl_4, material, master_standard_material</t>
+          <t>ms_bom_header, ms_bom_detail, product_lvl_4, material, master_standard_material</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>product_costing_header, product_costing_detail, material_cost, man_power_cost, bom_header, bom_detail, price_reference_header, price_reference_detail, flow_process_header, man_power_rate, rate_borongan_helper, rate_bahan_pendukung_foh, rate_generals, master_kurs, product_lvl_4</t>
+          <t>product_costing_header, product_costing_detail, material_cost, man_power_cost, ms_bom_header, ms_bom_detail, price_reference_header, price_reference_detail, flow_process_header, man_power_rate, rate_borongan_helper, rate_bahan_pendukung_foh, rate_generals, master_kurs, product_lvl_4</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -3150,7 +3150,7 @@
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>bom_header</t>
+          <t>ms_bom_header</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -3170,7 +3170,7 @@
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>bom_detail</t>
+          <t>ms_bom_detail</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">

--- a/specs/docs/workbook.xlsx
+++ b/specs/docs/workbook.xlsx
@@ -799,7 +799,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>FR-05 dan FR-06 (bagian Operator): Setelah unpacking, Operator melakukan Cek Kondisi Coil — pemeriksaan fisik (Manual task, dikecualikan dari UC, tanpa keterlibatan sistem). Bila hasilnya 'Tidak sesuai', Operator menginput Laporan Ketidaksesuaian Material ke sistem, yang kemudian dikirim ke Claim Material (proses lain, di luar Modul Produksi). [2026-10-26, FR-48 direvisi/FR-74] Saat Add SPK, setelah memilih produk, pengguna memilih varian BOM (kolom varian_type; label tampilan Varian BOM (varian_type)); dibawa ke item laporan (OQ 50-55). [2026-10-26, OQ 50/51/53/55 dijawab] SPK ditolak bila produk tanpa varian BOM atau Hasil Costing belum lengkap; varian per produk; varian dapat diubah selama SPK belum diinput laporan produksinya; SPK dibuat di modul Production Planning (eksternal). [2026-10-26, varian_type] Item Stok Bebas dan KW 2 pada laporan produksi mengikuti varian BOM yang dipilih di SPK; ERD yang diperbarui = erd-revisi.drawio.</t>
+          <t>FR-05 dan FR-06 (bagian Operator): Setelah unpacking, Operator melakukan Cek Kondisi Coil — pemeriksaan fisik (Manual task, dikecualikan dari UC, tanpa keterlibatan sistem). Bila hasilnya 'Tidak sesuai', Operator menginput Laporan Ketidaksesuaian Material ke sistem, yang kemudian dikirim ke Claim Material (proses lain, di luar Modul Produksi). [2026-10-26, FR-48 direvisi/FR-74] Saat Add SPK, setelah memilih produk, pengguna memilih varian BOM (kolom no_uniq_id; label tampilan Varian BOM (no_uniq_id)); dibawa ke item laporan (OQ 50-55). [2026-10-26, OQ 50/51/53/55 dijawab] SPK ditolak bila produk tanpa varian BOM atau Hasil Costing belum lengkap; varian per produk; varian dapat diubah selama SPK belum diinput laporan produksinya; SPK dibuat di modul Production Planning (eksternal). [2026-10-26, no_uniq_id] Item Stok Bebas dan KW 2 pada laporan produksi mengikuti varian BOM yang dipilih di SPK; ERD yang diperbarui = erd-revisi.drawio. [2026-10-26, direvisi] Kolom varian = ms_bom_detail.no_uniq_id (menggantikan varian_type; kunci pasangan id_produk + no_uniq_id).</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>FR-41, FR-51. Prasyarat: Master Produk (UC-N05), Master Material (UC-N06), Master Standard Material (UC-N15). 1) Engineering membuka daftar BOM per produk. 2) Engineering menambah varian BOM (Varian Tebal) untuk produk dengan memilih material dari Master Material. 3) Sistem menghitung Berat/Meter (kg/m) = ((Tebal Material − Standar Toleransi) × Lebar Coil × Standar Berat Jenis) + Coating dari Master Standard Material (global; satuan tidak ditampilkan, konversi dikalibrasi 0,14 mm × lebar 1219 × 7,85 ≈ 1,34 kg/m — FR-50) dan menyimpannya pada ms_bom_detail. 4) Sistem membuat No. Uniq ID per varian (mis. Type 001.1) dan mengisi Latest Update dan Updated By. 5) Engineering dapat View, Edit, atau Delete varian. Satu produk boleh memakai beberapa material, tetapi tidak boleh memakai material yang sama dua kali (unik produk + material). (Rev.1 UC-04; BPMN D05: 'Develop BOM Produk berdasarkan Varian Tebal'.)</t>
+          <t>FR-41, FR-51. Prasyarat: Master Produk (UC-N05), Master Material (UC-N06), Master Standard Material (UC-N15). 1) Engineering membuka daftar BOM per produk. 2) Engineering menambah varian BOM (Varian Tebal) untuk produk dengan memilih material dari Master Material. 3) Sistem menghitung Berat/Meter (kg/m) = ((Tebal Material − Standar Toleransi) × Lebar Coil × Standar Berat Jenis) + Coating dari Master Standard Material (global; satuan tidak ditampilkan, konversi dikalibrasi 0,14 mm × lebar 1219 × 7,85 ≈ 1,34 kg/m — FR-50) dan menyimpannya pada ms_bom_detail. 4) Sistem membuat No. Uniq ID per varian (mis. Type 001.1) dan mengisi Latest Update dan Updated By. 5) Engineering dapat View, Edit, atau Delete varian. Satu produk boleh memakai beberapa material, tetapi tidak boleh memakai material yang sama dua kali (unik produk + material). (Rev.1 UC-04; BPMN D05: 'Develop BOM Produk berdasarkan Varian Tebal'.) [2026-10-26, definisi varian] Satu varian = satu baris material pada BOM produk (ms_bom_detail); produk dengan beberapa material berbeda ketebalan punya beberapa varian; satu header ms_bom_header per produk (UNIQUE id_produk tetap); kunci varian = pasangan id_produk + no_uniq_id; ms_bom_header.varian_type dan is_default hanya kompatibilitas.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>menu Produksi (Daftar SPK, Input Produksi). Satu aktor, satu sitting, satu entitas (production_reports); 11 UC dalam satu halaman bersektor. Modul sudah ada (index, ajax_spk_list, create, ajax_get_coils, save, view). [2026-10-26, FR-48 direvisi/FR-74] Add SPK: pilih varian BOM setelah produk (kolom varian_type; label Varian BOM (varian_type)). [2026-10-26, OQ 50/51/53/55] SPK ditolak bila produk tanpa varian BOM/Hasil Costing lengkap; varian per produk; terkunci setelah laporan produksi diinput; Add SPK di mockup hanya simulasi modul Production Planning (eksternal).</t>
+          <t>menu Produksi (Daftar SPK, Input Produksi). Satu aktor, satu sitting, satu entitas (production_reports); 11 UC dalam satu halaman bersektor. Modul sudah ada (index, ajax_spk_list, create, ajax_get_coils, save, view). [2026-10-26, FR-48 direvisi/FR-74] Add SPK: pilih varian BOM setelah produk (kolom no_uniq_id; label Varian BOM (no_uniq_id)). [2026-10-26, OQ 50/51/53/55] SPK ditolak bila produk tanpa varian BOM/Hasil Costing lengkap; varian per produk; terkunci setelah laporan produksi diinput; Add SPK di mockup hanya simulasi modul Production Planning (eksternal). [2026-10-26, direvisi] Kolom varian = ms_bom_detail.no_uniq_id (menggantikan varian_type; kunci pasangan id_produk + no_uniq_id).</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
